--- a/docs/ABM_Intelligence_Account_Flow.xlsx
+++ b/docs/ABM_Intelligence_Account_Flow.xlsx
@@ -8,35 +8,38 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Account Flow" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Gates" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statuses" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scoring" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Touchpoints" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Integrations" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Configuration" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Example Walkthrough" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Glossary" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="General Flow" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Account Flow" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Gates" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statuses" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scoring" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Touchpoints" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Integrations" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Configuration" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Example Walkthrough" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Glossary" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Account Flow'!$A$4:$L$21</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Account Flow'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Decision Gates'!$A$4:$F$24</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Decision Gates'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Statuses'!$A$4:$E$24</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Statuses'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Scoring'!$A$4:$H$11</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Scoring'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Human Touchpoints'!$A$4:$F$19</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Human Touchpoints'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Integrations'!$A$4:$E$15</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Integrations'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Configuration'!$A$4:$D$35</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Configuration'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Example Walkthrough'!$A$4:$E$18</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="8">'Example Walkthrough'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Glossary'!$A$4:$B$26</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="9">'Glossary'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'General Flow'!$A$4:$G$16</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'General Flow'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Account Flow'!$A$4:$L$21</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Account Flow'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Decision Gates'!$A$4:$F$24</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Decision Gates'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Statuses'!$A$4:$E$24</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Statuses'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Scoring'!$A$4:$H$11</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Scoring'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Human Touchpoints'!$A$4:$F$19</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Human Touchpoints'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Integrations'!$A$4:$E$15</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Integrations'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Configuration'!$A$4:$D$35</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'Configuration'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Example Walkthrough'!$A$4:$E$18</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'Example Walkthrough'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Glossary'!$A$4:$B$26</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="10">'Glossary'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -45,7 +48,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -106,6 +109,12 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F2A44"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -193,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -229,6 +238,24 @@
     <xf numFmtId="0" fontId="10" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -238,12 +265,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -251,9 +272,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -272,9 +290,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -296,9 +311,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -666,7 +678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:B45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -820,254 +832,254 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>Account Flow</t>
+          <t>General Flow</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>The full flow, step by step: entry, 13 stages, outreach and hand-off. Start here.</t>
+          <t>The big picture in 12 phases, from data import to learning. Read this first.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>Decision Gates</t>
+          <t>Account Flow</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>Every check that can stop or redirect an account, with pass and fail outcomes.</t>
+          <t>The full flow, step by step: entry, 13 stages, outreach and hand-off. Start here.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>Statuses</t>
+          <t>Decision Gates</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Pipeline status and buying stage values, what they mean and how an account enters or leaves each.</t>
+          <t>Every check that can stop or redirect an account, with pass and fail outcomes.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>Scoring</t>
+          <t>Statuses</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Fit, data confidence, research priority, intent, engagement and priority: formula, inputs, thresholds.</t>
+          <t>Pipeline status and buying stage values, what they mean and how an account enters or leaves each.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>Human Touchpoints</t>
+          <t>Scoring</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Where a person must act, what they decide, and what happens if nobody acts.</t>
+          <t>Fit, data confidence, research priority, intent, engagement and priority: formula, inputs, thresholds.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>Integrations</t>
+          <t>Human Touchpoints</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>External services, which step uses each, and the rule that gates it.</t>
+          <t>Where a person must act, what they decide, and what happens if nobody acts.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Integrations</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Every threshold and setting, and whether it is fixed for all clients or set per client.</t>
+          <t>External services, which step uses each, and the rule that gates it.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>Example Walkthrough</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>One example company traced through every stage with the outcome at each step.</t>
+          <t>Every threshold and setting, and whether it is fixed for all clients or set per client.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
+          <t>Example Walkthrough</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>One example company traced through every stage with the outcome at each step.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
           <t>Glossary</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>Terms used in the application and this document.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="n"/>
-      <c r="B25" s="2" t="n"/>
-    </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="A26" s="2" t="n"/>
+      <c r="B26" s="2" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>Legend</t>
         </is>
       </c>
-      <c r="B26" s="2" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="B27" s="2" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>Entry</t>
         </is>
       </c>
-      <c r="B27" s="10" t="inlineStr">
+      <c r="B28" s="10" t="inlineStr">
         <is>
           <t>How a company gets into the system</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="11" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="B28" s="10" t="inlineStr">
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>Data intake, clean-up, fit and tier</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="12" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
         <is>
           <t>People</t>
         </is>
       </c>
-      <c r="B29" s="10" t="inlineStr">
+      <c r="B30" s="10" t="inlineStr">
         <is>
           <t>Identity checks, buying group, contact enrichment</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="13" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="13" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="B30" s="10" t="inlineStr">
+      <c r="B31" s="10" t="inlineStr">
         <is>
           <t>Research plan, evidence collection, account twin</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="14" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="14" t="inlineStr">
         <is>
           <t>Outreach</t>
         </is>
       </c>
-      <c r="B31" s="10" t="inlineStr">
+      <c r="B32" s="10" t="inlineStr">
         <is>
           <t>Readiness decision, drafting, approval</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="15" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="15" t="inlineStr">
         <is>
           <t>Engagement</t>
         </is>
       </c>
-      <c r="B32" s="10" t="inlineStr">
+      <c r="B33" s="10" t="inlineStr">
         <is>
           <t>Sending, signals, scoring, hand-off and learning</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="16" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>System</t>
         </is>
       </c>
-      <c r="B33" s="10" t="inlineStr">
+      <c r="B34" s="10" t="inlineStr">
         <is>
           <t>Done by fixed code rules</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="17" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="17" t="inlineStr">
         <is>
           <t>AI + rules</t>
         </is>
       </c>
-      <c r="B34" s="10" t="inlineStr">
+      <c r="B35" s="10" t="inlineStr">
         <is>
           <t>AI reads and labels sources; code rules decide</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="18" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="18" t="inlineStr">
         <is>
           <t>Human</t>
         </is>
       </c>
-      <c r="B35" s="10" t="inlineStr">
+      <c r="B36" s="10" t="inlineStr">
         <is>
           <t>A person decides or approves (also System + human, AI + human)</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="n"/>
-      <c r="B36" s="2" t="n"/>
-    </row>
     <row r="37">
-      <c r="A37" s="6" t="inlineStr">
+      <c r="A37" s="2" t="n"/>
+      <c r="B37" s="2" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>Core principles</t>
         </is>
       </c>
-      <c r="B37" s="2" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="19" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>Nothing is trusted on arrival: every field starts as unknown and keeps its source.</t>
-        </is>
-      </c>
+      <c r="B38" s="2" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="19" t="inlineStr">
@@ -1077,7 +1089,7 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>Unknown is not bad: missing firmographics lower data confidence, not fit.</t>
+          <t>Nothing is trusted on arrival: every field starts as unknown and keeps its source.</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1101,7 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>Spend follows value: cheap checks first, paid research and enrichment only for accounts that pass the gates.</t>
+          <t>Unknown is not bad: missing firmographics lower data confidence, not fit.</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1113,7 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>Every claim needs a source: drafts may only state facts that are verified or probable, fresh, and cited.</t>
+          <t>Spend follows value: cheap checks first, paid research and enrichment only for accounts that pass the gates.</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1125,7 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>AI reads, rules decide: the AI extracts and labels facts; scores and gates are fixed code rules.</t>
+          <t>Every claim needs a source: drafts may only state facts that are verified or probable, fresh, and cited.</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1137,7 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>People approve: rejections, lookalike approvals, identity conflicts and every outgoing email go to a person.</t>
+          <t>AI reads, rules decide: the AI extracts and labels facts; scores and gates are fixed code rules.</t>
         </is>
       </c>
     </row>
@@ -1136,6 +1148,18 @@
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>People approve: rejections, lookalike approvals, identity conflicts and every outgoing email go to a person.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="19" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
         <is>
           <t>No contact lookup before approval: Apollo people search runs only after a person approves the company.</t>
         </is>
@@ -1152,6 +1176,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
@@ -1159,6 +1184,425 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>Example Walkthrough</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="21" t="inlineStr">
+        <is>
+          <t>A hypothetical company traced through every stage with the Manch settings. The scores match the worked example in the scoring methodology document.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="22" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="B4" s="22" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C4" s="22" t="inlineStr">
+        <is>
+          <t>What the system sees</t>
+        </is>
+      </c>
+      <c r="D4" s="22" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="E4" s="22" t="inlineStr">
+        <is>
+          <t>Progress shown in the app</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="47" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="B5" s="25" t="inlineStr">
+        <is>
+          <t>CSV upload</t>
+        </is>
+      </c>
+      <c r="C5" s="25" t="inlineStr">
+        <is>
+          <t>Example Pharma Ltd, India, 8,000 employees, SAP S/4HANA + Power Apps; Head of Procurement among the people</t>
+        </is>
+      </c>
+      <c r="D5" s="25" t="inlineStr">
+        <is>
+          <t>Account and contacts created; journeys started</t>
+        </is>
+      </c>
+      <c r="E5" s="25" t="inlineStr">
+        <is>
+          <t>Imported</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="25" t="inlineStr">
+        <is>
+          <t>Data intake</t>
+        </is>
+      </c>
+      <c r="C6" s="25" t="inlineStr">
+        <is>
+          <t>Fields from the import, source = the file</t>
+        </is>
+      </c>
+      <c r="D6" s="25" t="inlineStr">
+        <is>
+          <t>All fields unknown until checked</t>
+        </is>
+      </c>
+      <c r="E6" s="25" t="inlineStr">
+        <is>
+          <t>Imported</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="25" t="inlineStr">
+        <is>
+          <t>Data clean-up</t>
+        </is>
+      </c>
+      <c r="C7" s="25" t="inlineStr">
+        <is>
+          <t>No duplicates</t>
+        </is>
+      </c>
+      <c r="D7" s="25" t="inlineStr">
+        <is>
+          <t>One account record</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="inlineStr">
+        <is>
+          <t>Data cleaned</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="25" t="inlineStr">
+        <is>
+          <t>Fit and tier</t>
+        </is>
+      </c>
+      <c r="C8" s="25" t="inlineStr">
+        <is>
+          <t>Size 18/25 (mid band), geography 15/15, tech 7/10; industry not scored</t>
+        </is>
+      </c>
+      <c r="D8" s="25" t="inlineStr">
+        <is>
+          <t>Fit 80; data confidence 0.61; research priority medium (58); tier T3 by size</t>
+        </is>
+      </c>
+      <c r="E8" s="25" t="inlineStr">
+        <is>
+          <t>Fit checked</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="25" t="inlineStr">
+        <is>
+          <t>Identity check</t>
+        </is>
+      </c>
+      <c r="C9" s="25" t="inlineStr">
+        <is>
+          <t>Head of Procurement: email, title, company agree</t>
+        </is>
+      </c>
+      <c r="D9" s="25" t="inlineStr">
+        <is>
+          <t>Identity verified</t>
+        </is>
+      </c>
+      <c r="E9" s="25" t="inlineStr">
+        <is>
+          <t>Contacts verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="25" t="inlineStr">
+        <is>
+          <t>Research plan</t>
+        </is>
+      </c>
+      <c r="C10" s="25" t="inlineStr">
+        <is>
+          <t>Unknown: current programmes, ownership of vendor data</t>
+        </is>
+      </c>
+      <c r="D10" s="25" t="inlineStr">
+        <is>
+          <t>2 questions per round (T3)</t>
+        </is>
+      </c>
+      <c r="E10" s="25" t="inlineStr">
+        <is>
+          <t>Research planned</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="25" t="inlineStr">
+        <is>
+          <t>Account research</t>
+        </is>
+      </c>
+      <c r="C11" s="25" t="inlineStr">
+        <is>
+          <t>SAP S/4HANA migration (2 sources); MDM lead job post (1 source)</t>
+        </is>
+      </c>
+      <c r="D11" s="25" t="inlineStr">
+        <is>
+          <t>Migration verified; job post probable</t>
+        </is>
+      </c>
+      <c r="E11" s="25" t="inlineStr">
+        <is>
+          <t>Researched</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="25" t="inlineStr">
+        <is>
+          <t>Twin and intent</t>
+        </is>
+      </c>
+      <c r="C12" s="25" t="inlineStr">
+        <is>
+          <t>Hypothesis linking migration and hiring validated; LinkedIn interest, pricing visit</t>
+        </is>
+      </c>
+      <c r="D12" s="25" t="inlineStr">
+        <is>
+          <t>Intent 83 (hot, 4 families) → tier upgraded T3 → T1, deep dive runs; priority 75</t>
+        </is>
+      </c>
+      <c r="E12" s="25" t="inlineStr">
+        <is>
+          <t>Facts confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="25" t="inlineStr">
+        <is>
+          <t>Buying group</t>
+        </is>
+      </c>
+      <c r="C13" s="25" t="inlineStr">
+        <is>
+          <t>Vendor-data problem → procurement and master-data personas</t>
+        </is>
+      </c>
+      <c r="D13" s="25" t="inlineStr">
+        <is>
+          <t>Head of Procurement = decision maker; Head of Master Data = champion</t>
+        </is>
+      </c>
+      <c r="E13" s="25" t="inlineStr">
+        <is>
+          <t>Buying group mapped</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="25" t="inlineStr">
+        <is>
+          <t>Contact enrichment</t>
+        </is>
+      </c>
+      <c r="C14" s="25" t="inlineStr">
+        <is>
+          <t>Email present; MX check passes</t>
+        </is>
+      </c>
+      <c r="D14" s="25" t="inlineStr">
+        <is>
+          <t>Outreach-ready</t>
+        </is>
+      </c>
+      <c r="E14" s="25" t="inlineStr">
+        <is>
+          <t>Contacts checked</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="25" t="inlineStr">
+        <is>
+          <t>Readiness</t>
+        </is>
+      </c>
+      <c r="C15" s="25" t="inlineStr">
+        <is>
+          <t>1 verified trigger in 90 days; identity ok; decision maker</t>
+        </is>
+      </c>
+      <c r="D15" s="25" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="E15" s="25" t="inlineStr">
+        <is>
+          <t>Ready for outreach</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="23" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="25" t="inlineStr">
+        <is>
+          <t>Draft and approve</t>
+        </is>
+      </c>
+      <c r="C16" s="25" t="inlineStr">
+        <is>
+          <t>Brief + cited migration fact + knowledge base (vendor onboarding use case, "mid-migration" objection)</t>
+        </is>
+      </c>
+      <c r="D16" s="25" t="inlineStr">
+        <is>
+          <t>Draft passes guardrails; user approves</t>
+        </is>
+      </c>
+      <c r="E16" s="25" t="inlineStr">
+        <is>
+          <t>Emails drafted</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="25" t="inlineStr">
+        <is>
+          <t>Send and score</t>
+        </is>
+      </c>
+      <c r="C17" s="25" t="inlineStr">
+        <is>
+          <t>Email sent; click, 2 opens, pricing visit, anonymous site visit</t>
+        </is>
+      </c>
+      <c r="D17" s="25" t="inlineStr">
+        <is>
+          <t>Engagement 35.3 → Engaged; next best action: call the Head of Procurement</t>
+        </is>
+      </c>
+      <c r="E17" s="25" t="inlineStr">
+        <is>
+          <t>In outreach</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="23" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="25" t="inlineStr">
+        <is>
+          <t>Hand-off</t>
+        </is>
+      </c>
+      <c r="C18" s="25" t="inlineStr">
+        <is>
+          <t>Prospect replies positively (or engagement reaches 70)</t>
+        </is>
+      </c>
+      <c r="D18" s="25" t="inlineStr">
+        <is>
+          <t>Hand-off with briefing; outreach paused; rep acknowledges within 24h</t>
+        </is>
+      </c>
+      <c r="E18" s="25" t="inlineStr">
+        <is>
+          <t>Handed to sales</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:E18"/>
+  <mergeCells count="1">
+    <mergeCell ref="A2:E2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1198,264 +1642,264 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Account</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>A target company.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>Seller profile</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>One client's settings: ideal customer profile, weights, targeting rule, triggers, personas, writing knowledge.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="45" t="inlineStr">
+      <c r="A7" s="47" t="inlineStr">
         <is>
           <t>ICP</t>
         </is>
       </c>
-      <c r="B7" s="26" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>Ideal customer profile: the kind of company the client sells to best.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="45" t="inlineStr">
+      <c r="A8" s="47" t="inlineStr">
         <is>
           <t>Fit</t>
         </is>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>How well a company matches the ICP, from firmographics only (0–100).</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="45" t="inlineStr">
+      <c r="A9" s="47" t="inlineStr">
         <is>
           <t>Tier</t>
         </is>
       </c>
-      <c r="B9" s="26" t="inlineStr">
+      <c r="B9" s="25" t="inlineStr">
         <is>
           <t>T1 / T2 / T3: how much research effort and budget a company gets.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="26" t="inlineStr">
+      <c r="A10" s="25" t="inlineStr">
         <is>
           <t>Trigger</t>
         </is>
       </c>
-      <c r="B10" s="26" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>A dated event that may create a need, e.g. an ERP migration, expansion or funding.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="26" t="inlineStr">
+      <c r="A11" s="25" t="inlineStr">
         <is>
           <t>Verified / probable</t>
         </is>
       </c>
-      <c r="B11" s="26" t="inlineStr">
+      <c r="B11" s="25" t="inlineStr">
         <is>
           <t>Verified: an official source or two independent sites. Probable: one credible source.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="26" t="inlineStr">
+      <c r="A12" s="25" t="inlineStr">
         <is>
           <t>Intent</t>
         </is>
       </c>
-      <c r="B12" s="26" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>Whether something is happening at the company now; rewards independent signals that agree.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="26" t="inlineStr">
+      <c r="A13" s="25" t="inlineStr">
         <is>
           <t>Signal family</t>
         </is>
       </c>
-      <c r="B13" s="26" t="inlineStr">
+      <c r="B13" s="25" t="inlineStr">
         <is>
           <t>A type of intent signal (trigger, programme, hiring, conversation, engagement…). Different families agreeing is convergence.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="26" t="inlineStr">
+      <c r="A14" s="25" t="inlineStr">
         <is>
           <t>Hypothesis</t>
         </is>
       </c>
-      <c r="B14" s="26" t="inlineStr">
+      <c r="B14" s="25" t="inlineStr">
         <is>
           <t>An AI-written explanation of how facts connect to a possible need; validated by a second pass that can only downgrade it.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="26" t="inlineStr">
+      <c r="A15" s="25" t="inlineStr">
         <is>
           <t>Account twin</t>
         </is>
       </c>
-      <c r="B15" s="26" t="inlineStr">
+      <c r="B15" s="25" t="inlineStr">
         <is>
           <t>The living, versioned view of an account: facts, inferences, contradictions, unknowns.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="26" t="inlineStr">
+      <c r="A16" s="25" t="inlineStr">
         <is>
           <t>Buying group</t>
         </is>
       </c>
-      <c r="B16" s="26" t="inlineStr">
+      <c r="B16" s="25" t="inlineStr">
         <is>
           <t>The people involved in a purchase: decision maker, champion, budget owner, influencer.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="26" t="inlineStr">
+      <c r="A17" s="25" t="inlineStr">
         <is>
           <t>Readiness</t>
         </is>
       </c>
-      <c r="B17" s="26" t="inlineStr">
+      <c r="B17" s="25" t="inlineStr">
         <is>
           <t>The decision whether a contact may be drafted to.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="26" t="inlineStr">
+      <c r="A18" s="25" t="inlineStr">
         <is>
           <t>Guardrails</t>
         </is>
       </c>
-      <c r="B18" s="26" t="inlineStr">
+      <c r="B18" s="25" t="inlineStr">
         <is>
           <t>Automatic checks on a draft: every claim cited, compliance lines present, quality rules.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="26" t="inlineStr">
+      <c r="A19" s="25" t="inlineStr">
         <is>
           <t>Engagement score</t>
         </is>
       </c>
-      <c r="B19" s="26" t="inlineStr">
+      <c r="B19" s="25" t="inlineStr">
         <is>
           <t>Points from activity, halving every 14 days, capped at 100.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="45" t="inlineStr">
+      <c r="A20" s="47" t="inlineStr">
         <is>
           <t>MQA</t>
         </is>
       </c>
-      <c r="B20" s="26" t="inlineStr">
+      <c r="B20" s="25" t="inlineStr">
         <is>
           <t>Marketing-qualified account: engagement of 70 or more; triggers a hand-off.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="26" t="inlineStr">
+      <c r="A21" s="25" t="inlineStr">
         <is>
           <t>Hand-off</t>
         </is>
       </c>
-      <c r="B21" s="26" t="inlineStr">
+      <c r="B21" s="25" t="inlineStr">
         <is>
           <t>Passing an engaged account to a sales rep with a fact-checked briefing; automation pauses.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="26" t="inlineStr">
+      <c r="A22" s="25" t="inlineStr">
         <is>
           <t>Watchlist</t>
         </is>
       </c>
-      <c r="B22" s="26" t="inlineStr">
+      <c r="B22" s="25" t="inlineStr">
         <is>
           <t>Accounts parked until a re-check date.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="26" t="inlineStr">
+      <c r="A23" s="25" t="inlineStr">
         <is>
           <t>Knowledge base</t>
         </is>
       </c>
-      <c r="B23" s="26" t="inlineStr">
+      <c r="B23" s="25" t="inlineStr">
         <is>
           <t>Playbook, personas, examples, case studies and learned emails the writer draws on.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="26" t="inlineStr">
+      <c r="A24" s="25" t="inlineStr">
         <is>
           <t>Lookalike</t>
         </is>
       </c>
-      <c r="B24" s="26" t="inlineStr">
+      <c r="B24" s="25" t="inlineStr">
         <is>
           <t>A company found because it resembles a reference company.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="26" t="inlineStr">
+      <c r="A25" s="25" t="inlineStr">
         <is>
           <t>Super Admin mode</t>
         </is>
       </c>
-      <c r="B25" s="26" t="inlineStr">
+      <c r="B25" s="25" t="inlineStr">
         <is>
           <t>View that shows every client's accounts; otherwise users see only accounts assigned to them.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="26" t="inlineStr">
+      <c r="A26" s="25" t="inlineStr">
         <is>
           <t>Background queue</t>
         </is>
       </c>
-      <c r="B26" s="26" t="inlineStr">
+      <c r="B26" s="25" t="inlineStr">
         <is>
           <t>The worker that runs the pipeline on queued companies, in slices of up to 5 minutes.</t>
         </is>
@@ -1472,6 +1916,505 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>General Flow</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="21" t="inlineStr">
+        <is>
+          <t>Data Import → Data Processing → Data Validation → Qualification → Identity Verification → Research → Analysis and Scoring → Buying Group and Enrichment → Readiness Check → Outreach → Engagement Tracking → Hand-off and Learning</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="22" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="22" t="inlineStr">
+        <is>
+          <t>Phase</t>
+        </is>
+      </c>
+      <c r="C4" s="22" t="inlineStr">
+        <is>
+          <t>Goal</t>
+        </is>
+      </c>
+      <c r="D4" s="22" t="inlineStr">
+        <is>
+          <t>What happens</t>
+        </is>
+      </c>
+      <c r="E4" s="22" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="F4" s="22" t="inlineStr">
+        <is>
+          <t>Detailed stages</t>
+        </is>
+      </c>
+      <c r="G4" s="22" t="inlineStr">
+        <is>
+          <t>Done by</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>Data Import</t>
+        </is>
+      </c>
+      <c r="C5" s="25" t="inlineStr">
+        <is>
+          <t>Bring companies and people into the system</t>
+        </is>
+      </c>
+      <c r="D5" s="25" t="inlineStr">
+        <is>
+          <t>CSV upload, Lookalikes (AI-found, human-approved), Apollo website visitors, manual add</t>
+        </is>
+      </c>
+      <c r="E5" s="25" t="inlineStr">
+        <is>
+          <t>Account and contact records, linked; import batch</t>
+        </is>
+      </c>
+      <c r="F5" s="25" t="inlineStr">
+        <is>
+          <t>Entry, stage 1</t>
+        </is>
+      </c>
+      <c r="G5" s="26" t="inlineStr">
+        <is>
+          <t>System + human</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>Data Processing</t>
+        </is>
+      </c>
+      <c r="C6" s="25" t="inlineStr">
+        <is>
+          <t>Make the data usable</t>
+        </is>
+      </c>
+      <c r="D6" s="25" t="inlineStr">
+        <is>
+          <t>Clean and normalise fields (names, countries, sizes, URLs); merge duplicates without deleting; link people to companies</t>
+        </is>
+      </c>
+      <c r="E6" s="25" t="inlineStr">
+        <is>
+          <t>One clean record per company and per person</t>
+        </is>
+      </c>
+      <c r="F6" s="25" t="inlineStr">
+        <is>
+          <t>Stage 2</t>
+        </is>
+      </c>
+      <c r="G6" s="27" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>Data Validation</t>
+        </is>
+      </c>
+      <c r="C7" s="25" t="inlineStr">
+        <is>
+          <t>Know what can be trusted</t>
+        </is>
+      </c>
+      <c r="D7" s="25" t="inlineStr">
+        <is>
+          <t>Every field starts as unknown; malformed fields marked invalid; exclusions (customer, open deal, do-not-contact, recent loss) and the client's hard targeting rule checked</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="inlineStr">
+        <is>
+          <t>Field statuses; excluded or stopped companies with reasons</t>
+        </is>
+      </c>
+      <c r="F7" s="25" t="inlineStr">
+        <is>
+          <t>Stages 2-3</t>
+        </is>
+      </c>
+      <c r="G7" s="27" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="C8" s="25" t="inlineStr">
+        <is>
+          <t>Decide who deserves effort and spend</t>
+        </is>
+      </c>
+      <c r="D8" s="25" t="inlineStr">
+        <is>
+          <t>Fit score against the client's ICP; fit floor 40; data confidence; tier (T1/T2/T3); research priority</t>
+        </is>
+      </c>
+      <c r="E8" s="25" t="inlineStr">
+        <is>
+          <t>Fit, tier, priority; low fit proposed for rejection</t>
+        </is>
+      </c>
+      <c r="F8" s="25" t="inlineStr">
+        <is>
+          <t>Stage 3</t>
+        </is>
+      </c>
+      <c r="G8" s="26" t="inlineStr">
+        <is>
+          <t>System + human</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>Identity Verification</t>
+        </is>
+      </c>
+      <c r="C9" s="25" t="inlineStr">
+        <is>
+          <t>Make sure each person is real and current</t>
+        </is>
+      </c>
+      <c r="D9" s="25" t="inlineStr">
+        <is>
+          <t>Email, title, company, phone and LinkedIn checked against sources; conflicts re-checked once, then a person decides</t>
+        </is>
+      </c>
+      <c r="E9" s="25" t="inlineStr">
+        <is>
+          <t>Verified / probable / conflicting per field</t>
+        </is>
+      </c>
+      <c r="F9" s="25" t="inlineStr">
+        <is>
+          <t>Stage 4</t>
+        </is>
+      </c>
+      <c r="G9" s="26" t="inlineStr">
+        <is>
+          <t>System + human</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="C10" s="25" t="inlineStr">
+        <is>
+          <t>Find out what is happening at the company</t>
+        </is>
+      </c>
+      <c r="D10" s="25" t="inlineStr">
+        <is>
+          <t>Plan only questions that change a decision; search the web (Exa, Tavily, SerpAPI); AI extracts facts with source and date; verified = official or 2 independent sources</t>
+        </is>
+      </c>
+      <c r="E10" s="25" t="inlineStr">
+        <is>
+          <t>Source-backed facts and negative news</t>
+        </is>
+      </c>
+      <c r="F10" s="25" t="inlineStr">
+        <is>
+          <t>Stages 5-6</t>
+        </is>
+      </c>
+      <c r="G10" s="28" t="inlineStr">
+        <is>
+          <t>AI + rules</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>Analysis and Scoring</t>
+        </is>
+      </c>
+      <c r="C11" s="25" t="inlineStr">
+        <is>
+          <t>Turn facts into a view and a priority</t>
+        </is>
+      </c>
+      <c r="D11" s="25" t="inlineStr">
+        <is>
+          <t>Account twin (facts vs inferences); AI hypotheses validated; intent scored; hot intent upgrades to T1; priority score and next best action</t>
+        </is>
+      </c>
+      <c r="E11" s="25" t="inlineStr">
+        <is>
+          <t>Brief, intent (hot/warm/cold), priority 0-100</t>
+        </is>
+      </c>
+      <c r="F11" s="25" t="inlineStr">
+        <is>
+          <t>Stage 7</t>
+        </is>
+      </c>
+      <c r="G11" s="28" t="inlineStr">
+        <is>
+          <t>AI + rules</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>Buying Group and Enrichment</t>
+        </is>
+      </c>
+      <c r="C12" s="25" t="inlineStr">
+        <is>
+          <t>Find the right people to contact</t>
+        </is>
+      </c>
+      <c r="D12" s="25" t="inlineStr">
+        <is>
+          <t>Map decision maker, champion, budget owner, influencer by the problem; fill only missing contact data (Apollo, approval-gated); suppression and lawful basis</t>
+        </is>
+      </c>
+      <c r="E12" s="25" t="inlineStr">
+        <is>
+          <t>Outreach-ready contacts</t>
+        </is>
+      </c>
+      <c r="F12" s="25" t="inlineStr">
+        <is>
+          <t>Stages 8-9</t>
+        </is>
+      </c>
+      <c r="G12" s="27" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>Readiness Check</t>
+        </is>
+      </c>
+      <c r="C13" s="25" t="inlineStr">
+        <is>
+          <t>Stop weak intelligence from becoming email</t>
+        </is>
+      </c>
+      <c r="D13" s="25" t="inlineStr">
+        <is>
+          <t>Negative news, evidence strength (1 verified or 2 independent triggers in 90 days), identity, lawful basis, deliverability, role</t>
+        </is>
+      </c>
+      <c r="E13" s="25" t="inlineStr">
+        <is>
+          <t>Ready, research again, watch, review or disqualified</t>
+        </is>
+      </c>
+      <c r="F13" s="25" t="inlineStr">
+        <is>
+          <t>Stage 10</t>
+        </is>
+      </c>
+      <c r="G13" s="27" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>Outreach</t>
+        </is>
+      </c>
+      <c r="C14" s="25" t="inlineStr">
+        <is>
+          <t>Contact the buying group with relevant, cited messages</t>
+        </is>
+      </c>
+      <c r="D14" s="25" t="inlineStr">
+        <is>
+          <t>AI drafts from facts and the knowledge base; guardrails check claims and compliance; a person approves every email; safe sending with caps</t>
+        </is>
+      </c>
+      <c r="E14" s="25" t="inlineStr">
+        <is>
+          <t>Approved and sent emails, LinkedIn tasks</t>
+        </is>
+      </c>
+      <c r="F14" s="25" t="inlineStr">
+        <is>
+          <t>Stages 11-12</t>
+        </is>
+      </c>
+      <c r="G14" s="26" t="inlineStr">
+        <is>
+          <t>AI + human</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="23" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>Engagement Tracking</t>
+        </is>
+      </c>
+      <c r="C15" s="25" t="inlineStr">
+        <is>
+          <t>See who responds and how much</t>
+        </is>
+      </c>
+      <c r="D15" s="25" t="inlineStr">
+        <is>
+          <t>Opens, clicks, replies, site and pricing visits become signals; engagement score (14-day decay) and buying stage updated; intent re-read</t>
+        </is>
+      </c>
+      <c r="E15" s="25" t="inlineStr">
+        <is>
+          <t>Engagement score; Aware / Engaged / MQA</t>
+        </is>
+      </c>
+      <c r="F15" s="25" t="inlineStr">
+        <is>
+          <t>Stage 12</t>
+        </is>
+      </c>
+      <c r="G15" s="27" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>Hand-off and Learning</t>
+        </is>
+      </c>
+      <c r="C16" s="25" t="inlineStr">
+        <is>
+          <t>Pass engaged accounts to sales and improve</t>
+        </is>
+      </c>
+      <c r="D16" s="25" t="inlineStr">
+        <is>
+          <t>MQA (70) or positive reply → hand-off with briefing, outreach paused, rep acknowledges in 24h; outcomes recorded; winning emails saved to the knowledge base; lost deals return via the watchlist</t>
+        </is>
+      </c>
+      <c r="E16" s="25" t="inlineStr">
+        <is>
+          <t>Opportunity in CRM; outcome; learned examples</t>
+        </is>
+      </c>
+      <c r="F16" s="25" t="inlineStr">
+        <is>
+          <t>Stage 13</t>
+        </is>
+      </c>
+      <c r="G16" s="26" t="inlineStr">
+        <is>
+          <t>System + human</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:G16"/>
+  <mergeCells count="1">
+    <mergeCell ref="A2:G2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1571,1028 +2514,1028 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="23" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>E1</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>Entry</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="31" t="inlineStr">
         <is>
           <t>CSV upload</t>
         </is>
       </c>
-      <c r="D5" s="24" t="inlineStr">
+      <c r="D5" s="30" t="inlineStr">
         <is>
           <t>Bring in companies and people the team already has.</t>
         </is>
       </c>
-      <c r="E5" s="26" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t>CSV file (up to 50 MB), campaign and sender chosen by the user</t>
         </is>
       </c>
-      <c r="F5" s="26" t="inlineStr">
+      <c r="F5" s="25" t="inlineStr">
         <is>
           <t>User maps columns once (company, people, optional LinkedIn activity), previews matches, confirms. Rows are saved in chunks; companies and people are linked; each person's journey starts.</t>
         </is>
       </c>
-      <c r="G5" s="26" t="inlineStr">
+      <c r="G5" s="25" t="inlineStr">
         <is>
           <t>Re-upload updates existing records, never duplicates. Rows failing validation are rejected with a reason. Matching: LinkedIn URL, then email, then name within company.</t>
         </is>
       </c>
-      <c r="H5" s="27" t="inlineStr">
+      <c r="H5" s="26" t="inlineStr">
         <is>
           <t>System + human</t>
         </is>
       </c>
-      <c r="I5" s="26" t="inlineStr">
+      <c r="I5" s="25" t="inlineStr">
         <is>
           <t>Account and contact records, journeys, an import batch</t>
         </is>
       </c>
-      <c r="J5" s="26" t="inlineStr">
+      <c r="J5" s="25" t="inlineStr">
         <is>
           <t>Stage 1, then the background queue researches new and changed companies</t>
         </is>
       </c>
-      <c r="K5" s="26" t="inlineStr">
+      <c r="K5" s="25" t="inlineStr">
         <is>
           <t>Rejected rows listed with reasons; upload the corrected file again</t>
         </is>
       </c>
-      <c r="L5" s="26" t="inlineStr">
+      <c r="L5" s="25" t="inlineStr">
         <is>
           <t>Import → Upload CSV</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="23" t="inlineStr">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>E2</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>Entry</t>
         </is>
       </c>
-      <c r="C6" s="25" t="inlineStr">
+      <c r="C6" s="31" t="inlineStr">
         <is>
           <t>Lookalikes</t>
         </is>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="30" t="inlineStr">
         <is>
           <t>Find new companies similar to a reference company.</t>
         </is>
       </c>
-      <c r="E6" s="26" t="inlineStr">
+      <c r="E6" s="25" t="inlineStr">
         <is>
           <t>A reference website</t>
         </is>
       </c>
-      <c r="F6" s="26" t="inlineStr">
+      <c r="F6" s="25" t="inlineStr">
         <is>
           <t>AI finds candidates (Exa, Tavily), investigates each in rounds, rates five dimensions from evidence, assigns readiness. A person approves, rejects or asks for more research.</t>
         </is>
       </c>
-      <c r="G6" s="26" t="inlineStr">
+      <c r="G6" s="25" t="inlineStr">
         <is>
           <t>Recommended from lookalike fit 55 (per client). No verified facts caps fit at 50. Ready needs a verified buying event. Apollo is not called before approval.</t>
         </is>
       </c>
-      <c r="H6" s="27" t="inlineStr">
+      <c r="H6" s="26" t="inlineStr">
         <is>
           <t>AI + human</t>
         </is>
       </c>
-      <c r="I6" s="26" t="inlineStr">
+      <c r="I6" s="25" t="inlineStr">
         <is>
           <t>Suggestion with fit, readiness, reasons and evidence</t>
         </is>
       </c>
-      <c r="J6" s="26" t="inlineStr">
+      <c r="J6" s="25" t="inlineStr">
         <is>
           <t>On approval: becomes an account, enters stage 1; Apollo may now find decision makers</t>
         </is>
       </c>
-      <c r="K6" s="26" t="inlineStr">
+      <c r="K6" s="25" t="inlineStr">
         <is>
           <t>Rejected (with reason) or excluded by the targeting rule</t>
         </is>
       </c>
-      <c r="L6" s="26" t="inlineStr">
+      <c r="L6" s="25" t="inlineStr">
         <is>
           <t>Import → Lookalikes</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="23" t="inlineStr">
+      <c r="A7" s="29" t="inlineStr">
         <is>
           <t>E3</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>Entry</t>
         </is>
       </c>
-      <c r="C7" s="25" t="inlineStr">
+      <c r="C7" s="31" t="inlineStr">
         <is>
           <t>Apollo website visitors</t>
         </is>
       </c>
-      <c r="D7" s="24" t="inlineStr">
+      <c r="D7" s="30" t="inlineStr">
         <is>
           <t>Turn companies visiting the client's website into accounts.</t>
         </is>
       </c>
-      <c r="E7" s="26" t="inlineStr">
+      <c r="E7" s="25" t="inlineStr">
         <is>
           <t>Apollo visitor feed</t>
         </is>
       </c>
-      <c r="F7" s="26" t="inlineStr">
+      <c r="F7" s="25" t="inlineStr">
         <is>
           <t>Known companies are matched; unknown companies are kept as suggestions for Discover.</t>
         </is>
       </c>
-      <c r="G7" s="26" t="inlineStr">
+      <c r="G7" s="25" t="inlineStr">
         <is>
           <t>Same targeting rules as any account.</t>
         </is>
       </c>
-      <c r="H7" s="27" t="inlineStr">
+      <c r="H7" s="26" t="inlineStr">
         <is>
           <t>System + human</t>
         </is>
       </c>
-      <c r="I7" s="26" t="inlineStr">
+      <c r="I7" s="25" t="inlineStr">
         <is>
           <t>Suggestions or matched accounts with web-visit signals</t>
         </is>
       </c>
-      <c r="J7" s="26" t="inlineStr">
+      <c r="J7" s="25" t="inlineStr">
         <is>
           <t>Approved suggestions enter stage 1</t>
         </is>
       </c>
-      <c r="K7" s="26" t="inlineStr">
+      <c r="K7" s="25" t="inlineStr">
         <is>
           <t>Left as a suggestion</t>
         </is>
       </c>
-      <c r="L7" s="26" t="inlineStr">
+      <c r="L7" s="25" t="inlineStr">
         <is>
           <t>Import → Via Apollo; Discover</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="23" t="inlineStr">
+      <c r="A8" s="29" t="inlineStr">
         <is>
           <t>E4</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>Entry</t>
         </is>
       </c>
-      <c r="C8" s="25" t="inlineStr">
+      <c r="C8" s="31" t="inlineStr">
         <is>
           <t>Manual add</t>
         </is>
       </c>
-      <c r="D8" s="24" t="inlineStr">
+      <c r="D8" s="30" t="inlineStr">
         <is>
           <t>Add a single company by hand.</t>
         </is>
       </c>
-      <c r="E8" s="26" t="inlineStr">
+      <c r="E8" s="25" t="inlineStr">
         <is>
           <t>Name and website</t>
         </is>
       </c>
-      <c r="F8" s="26" t="inlineStr">
+      <c r="F8" s="25" t="inlineStr">
         <is>
           <t>Super Admin or user adds the company (optionally a logo URL).</t>
         </is>
       </c>
-      <c r="G8" s="26" t="inlineStr">
+      <c r="G8" s="25" t="inlineStr">
         <is>
           <t>Same as CSV.</t>
         </is>
       </c>
-      <c r="H8" s="27" t="inlineStr">
+      <c r="H8" s="26" t="inlineStr">
         <is>
           <t>Human</t>
         </is>
       </c>
-      <c r="I8" s="26" t="inlineStr">
+      <c r="I8" s="25" t="inlineStr">
         <is>
           <t>One account</t>
         </is>
       </c>
-      <c r="J8" s="26" t="inlineStr">
+      <c r="J8" s="25" t="inlineStr">
         <is>
           <t>Stage 1</t>
         </is>
       </c>
-      <c r="K8" s="26" t="inlineStr">
+      <c r="K8" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L8" s="26" t="inlineStr">
+      <c r="L8" s="25" t="inlineStr">
         <is>
           <t>Companies → New company</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="28" t="n">
+      <c r="A9" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="29" t="inlineStr">
+      <c r="B9" s="33" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C9" s="30" t="inlineStr">
+      <c r="C9" s="34" t="inlineStr">
         <is>
           <t>Data intake</t>
         </is>
       </c>
-      <c r="D9" s="29" t="inlineStr">
+      <c r="D9" s="33" t="inlineStr">
         <is>
           <t>Accept uploaded or connected data without assuming any of it is correct.</t>
         </is>
       </c>
-      <c r="E9" s="26" t="inlineStr">
+      <c r="E9" s="25" t="inlineStr">
         <is>
           <t>CSV, CRM form, API</t>
         </is>
       </c>
-      <c r="F9" s="26" t="inlineStr">
+      <c r="F9" s="25" t="inlineStr">
         <is>
           <t>Records are received and stored with their source. Every field starts as unknown.</t>
         </is>
       </c>
-      <c r="G9" s="26" t="inlineStr">
+      <c r="G9" s="25" t="inlineStr">
         <is>
           <t>Nothing is trusted yet.</t>
         </is>
       </c>
-      <c r="H9" s="31" t="inlineStr">
+      <c r="H9" s="27" t="inlineStr">
         <is>
           <t>System</t>
         </is>
       </c>
-      <c r="I9" s="26" t="inlineStr">
+      <c r="I9" s="25" t="inlineStr">
         <is>
           <t>Raw account and contact records</t>
         </is>
       </c>
-      <c r="J9" s="26" t="inlineStr">
+      <c r="J9" s="25" t="inlineStr">
         <is>
           <t>Stage 2</t>
         </is>
       </c>
-      <c r="K9" s="26" t="inlineStr">
+      <c r="K9" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L9" s="26" t="inlineStr">
+      <c r="L9" s="25" t="inlineStr">
         <is>
           <t>Behind the scenes (pipeline log)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="28" t="n">
+      <c r="A10" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="B10" s="29" t="inlineStr">
+      <c r="B10" s="33" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C10" s="30" t="inlineStr">
+      <c r="C10" s="34" t="inlineStr">
         <is>
           <t>Data clean-up</t>
         </is>
       </c>
-      <c r="D10" s="29" t="inlineStr">
+      <c r="D10" s="33" t="inlineStr">
         <is>
           <t>Fix obvious data problems before spending money.</t>
         </is>
       </c>
-      <c r="E10" s="26" t="inlineStr">
+      <c r="E10" s="25" t="inlineStr">
         <is>
           <t>records.received</t>
         </is>
       </c>
-      <c r="F10" s="26" t="inlineStr">
+      <c r="F10" s="25" t="inlineStr">
         <is>
           <t>Duplicates are merged (never deleted); malformed fields are marked invalid.</t>
         </is>
       </c>
-      <c r="G10" s="26" t="inlineStr">
+      <c r="G10" s="25" t="inlineStr">
         <is>
           <t>Merge keeps history; invalid fields are not used later.</t>
         </is>
       </c>
-      <c r="H10" s="31" t="inlineStr">
+      <c r="H10" s="27" t="inlineStr">
         <is>
           <t>System</t>
         </is>
       </c>
-      <c r="I10" s="26" t="inlineStr">
+      <c r="I10" s="25" t="inlineStr">
         <is>
           <t>One canonical account and person record each</t>
         </is>
       </c>
-      <c r="J10" s="26" t="inlineStr">
+      <c r="J10" s="25" t="inlineStr">
         <is>
           <t>Stage 3</t>
         </is>
       </c>
-      <c r="K10" s="26" t="inlineStr">
+      <c r="K10" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L10" s="26" t="inlineStr">
+      <c r="L10" s="25" t="inlineStr">
         <is>
           <t>Company page → History</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="28" t="n">
+      <c r="A11" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="B11" s="29" t="inlineStr">
+      <c r="B11" s="33" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C11" s="30" t="inlineStr">
+      <c r="C11" s="34" t="inlineStr">
         <is>
           <t>Fit and tier</t>
         </is>
       </c>
-      <c r="D11" s="29" t="inlineStr">
+      <c r="D11" s="33" t="inlineStr">
         <is>
           <t>Decide which accounts deserve spend, before any paid check.</t>
         </is>
       </c>
-      <c r="E11" s="26" t="inlineStr">
+      <c r="E11" s="25" t="inlineStr">
         <is>
           <t>records.cleaned</t>
         </is>
       </c>
-      <c r="F11" s="26" t="inlineStr">
+      <c r="F11" s="25" t="inlineStr">
         <is>
           <t>Exclusions checked; hard targeting rule checked; fit scored; data confidence, tier and research priority set.</t>
         </is>
       </c>
-      <c r="G11" s="26" t="inlineStr">
+      <c r="G11" s="25" t="inlineStr">
         <is>
           <t>Customer / open deal → sales owns it. Do-not-contact → disqualified. Lost deal &lt; 90 days → watch. Targeting rule (Manch: India, &gt; 5,000 employees). Fit floor 40. Tier by size (Manch: T1 ≥ 50,000, T2 ≥ 15,000) or by fit (T1 ≥ 80, T2 ≥ 60).</t>
         </is>
       </c>
-      <c r="H11" s="31" t="inlineStr">
+      <c r="H11" s="27" t="inlineStr">
         <is>
           <t>System</t>
         </is>
       </c>
-      <c r="I11" s="26" t="inlineStr">
+      <c r="I11" s="25" t="inlineStr">
         <is>
           <t>Fit score and reasons, tier, data confidence, research priority</t>
         </is>
       </c>
-      <c r="J11" s="26" t="inlineStr">
+      <c r="J11" s="25" t="inlineStr">
         <is>
           <t>Stage 4</t>
         </is>
       </c>
-      <c r="K11" s="26" t="inlineStr">
+      <c r="K11" s="25" t="inlineStr">
         <is>
           <t>Proposed rejection (a person confirms); missing country or size → run stops and asks for it in the next upload</t>
         </is>
       </c>
-      <c r="L11" s="26" t="inlineStr">
+      <c r="L11" s="25" t="inlineStr">
         <is>
           <t>Companies list; company page → Fit</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="32" t="n">
+      <c r="A12" s="35" t="n">
         <v>4</v>
       </c>
-      <c r="B12" s="33" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>People</t>
         </is>
       </c>
-      <c r="C12" s="34" t="inlineStr">
+      <c r="C12" s="37" t="inlineStr">
         <is>
           <t>Identity check</t>
         </is>
       </c>
-      <c r="D12" s="33" t="inlineStr">
+      <c r="D12" s="36" t="inlineStr">
         <is>
           <t>Check that email, company, title, phone and LinkedIn belong to the same current person.</t>
         </is>
       </c>
-      <c r="E12" s="26" t="inlineStr">
+      <c r="E12" s="25" t="inlineStr">
         <is>
           <t>account.prioritized</t>
         </is>
       </c>
-      <c r="F12" s="26" t="inlineStr">
+      <c r="F12" s="25" t="inlineStr">
         <is>
           <t>Each person's fields are checked against sources and marked verified, probable, stale, conflicting or invalid.</t>
         </is>
       </c>
-      <c r="G12" s="26" t="inlineStr">
+      <c r="G12" s="25" t="inlineStr">
         <is>
           <t>Conflicting fields get one focused re-check; still conflicting → a person decides. Any email domain is accepted (no company-domain requirement).</t>
         </is>
       </c>
-      <c r="H12" s="27" t="inlineStr">
+      <c r="H12" s="26" t="inlineStr">
         <is>
           <t>System + human</t>
         </is>
       </c>
-      <c r="I12" s="26" t="inlineStr">
+      <c r="I12" s="25" t="inlineStr">
         <is>
           <t>Field statuses and identity confidence per person</t>
         </is>
       </c>
-      <c r="J12" s="26" t="inlineStr">
+      <c r="J12" s="25" t="inlineStr">
         <is>
           <t>Stage 5</t>
         </is>
       </c>
-      <c r="K12" s="26" t="inlineStr">
+      <c r="K12" s="25" t="inlineStr">
         <is>
           <t>Conflict → review queue</t>
         </is>
       </c>
-      <c r="L12" s="26" t="inlineStr">
+      <c r="L12" s="25" t="inlineStr">
         <is>
           <t>People; Approvals</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="35" t="n">
+      <c r="A13" s="38" t="n">
         <v>5</v>
       </c>
-      <c r="B13" s="36" t="inlineStr">
+      <c r="B13" s="39" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="C13" s="37" t="inlineStr">
+      <c r="C13" s="40" t="inlineStr">
         <is>
           <t>Research plan</t>
         </is>
       </c>
-      <c r="D13" s="36" t="inlineStr">
+      <c r="D13" s="39" t="inlineStr">
         <is>
           <t>Turn gaps into a short list of questions that change a decision.</t>
         </is>
       </c>
-      <c r="E13" s="26" t="inlineStr">
+      <c r="E13" s="25" t="inlineStr">
         <is>
           <t>identity.checked, watchlist re-check, intent surge</t>
         </is>
       </c>
-      <c r="F13" s="26" t="inlineStr">
+      <c r="F13" s="25" t="inlineStr">
         <is>
           <t>The brain lists what is unknown and only plans questions whose answer would change a decision.</t>
         </is>
       </c>
-      <c r="G13" s="26" t="inlineStr">
+      <c r="G13" s="25" t="inlineStr">
         <is>
           <t>Already known and fresh → skipped. Questions per round by tier: T1 3, T2 3, T3 2.</t>
         </is>
       </c>
-      <c r="H13" s="38" t="inlineStr">
+      <c r="H13" s="28" t="inlineStr">
         <is>
           <t>AI + rules</t>
         </is>
       </c>
-      <c r="I13" s="26" t="inlineStr">
+      <c r="I13" s="25" t="inlineStr">
         <is>
           <t>Research plan with questions and skipped items</t>
         </is>
       </c>
-      <c r="J13" s="26" t="inlineStr">
+      <c r="J13" s="25" t="inlineStr">
         <is>
           <t>Stage 6</t>
         </is>
       </c>
-      <c r="K13" s="26" t="inlineStr">
+      <c r="K13" s="25" t="inlineStr">
         <is>
           <t>Budget reached → stops with reason</t>
         </is>
       </c>
-      <c r="L13" s="26" t="inlineStr">
+      <c r="L13" s="25" t="inlineStr">
         <is>
           <t>Company page → Research</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="35" t="n">
+      <c r="A14" s="38" t="n">
         <v>6</v>
       </c>
-      <c r="B14" s="36" t="inlineStr">
+      <c r="B14" s="39" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="C14" s="37" t="inlineStr">
+      <c r="C14" s="40" t="inlineStr">
         <is>
           <t>Account research</t>
         </is>
       </c>
-      <c r="D14" s="36" t="inlineStr">
+      <c r="D14" s="39" t="inlineStr">
         <is>
           <t>Collect source-backed evidence, cheapest strong sources first.</t>
         </is>
       </c>
-      <c r="E14" s="26" t="inlineStr">
+      <c r="E14" s="25" t="inlineStr">
         <is>
           <t>research.planned</t>
         </is>
       </c>
-      <c r="F14" s="26" t="inlineStr">
+      <c r="F14" s="25" t="inlineStr">
         <is>
           <t>Search (Exa, Tavily, SerpAPI) → AI reads pages and extracts claims with a quote, source and date. Facts become verified (official source or 2 independent sites) or probable (1 source). Negative news is collected too.</t>
         </is>
       </c>
-      <c r="G14" s="26" t="inlineStr">
+      <c r="G14" s="25" t="inlineStr">
         <is>
           <t>One main pass and at most one targeted follow-up. Investigation rounds by tier: T1 4, T2 3, T3 2. Budget per company: T1 $5, T2 $2, T3 $0.75. Search results cached 48h.</t>
         </is>
       </c>
-      <c r="H14" s="38" t="inlineStr">
+      <c r="H14" s="28" t="inlineStr">
         <is>
           <t>AI + rules</t>
         </is>
       </c>
-      <c r="I14" s="26" t="inlineStr">
+      <c r="I14" s="25" t="inlineStr">
         <is>
           <t>Facts and negative evidence, each with source and date</t>
         </is>
       </c>
-      <c r="J14" s="26" t="inlineStr">
+      <c r="J14" s="25" t="inlineStr">
         <is>
           <t>Stage 7</t>
         </is>
       </c>
-      <c r="K14" s="26" t="inlineStr">
+      <c r="K14" s="25" t="inlineStr">
         <is>
           <t>No evidence → recorded as unknown (not as "no")</t>
         </is>
       </c>
-      <c r="L14" s="26" t="inlineStr">
+      <c r="L14" s="25" t="inlineStr">
         <is>
           <t>Company page → Evidence; Signals</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="35" t="n">
+      <c r="A15" s="38" t="n">
         <v>7</v>
       </c>
-      <c r="B15" s="36" t="inlineStr">
+      <c r="B15" s="39" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="C15" s="37" t="inlineStr">
+      <c r="C15" s="40" t="inlineStr">
         <is>
           <t>Account twin and intent</t>
         </is>
       </c>
-      <c r="D15" s="36" t="inlineStr">
+      <c r="D15" s="39" t="inlineStr">
         <is>
           <t>Keep one living view of the account, separating facts from inference.</t>
         </is>
       </c>
-      <c r="E15" s="26" t="inlineStr">
+      <c r="E15" s="25" t="inlineStr">
         <is>
           <t>research.done</t>
         </is>
       </c>
-      <c r="F15" s="26" t="inlineStr">
+      <c r="F15" s="25" t="inlineStr">
         <is>
           <t>Facts, inferences, contradictions and unknowns are stored as a versioned twin. AI writes hypotheses; a second AI pass validates and can only lower a class. Intent is scored.</t>
         </is>
       </c>
-      <c r="G15" s="26" t="inlineStr">
+      <c r="G15" s="25" t="inlineStr">
         <is>
           <t>Official source wins a contradiction; otherwise reopens once, then a person decides. Hot intent (≥ 65 and 2+ independent signal families) upgrades the tier to T1 and runs the deep dive.</t>
         </is>
       </c>
-      <c r="H15" s="38" t="inlineStr">
+      <c r="H15" s="28" t="inlineStr">
         <is>
           <t>AI + rules</t>
         </is>
       </c>
-      <c r="I15" s="26" t="inlineStr">
+      <c r="I15" s="25" t="inlineStr">
         <is>
           <t>Versioned twin, investigation conclusions, intent reading, priority score, strategist brief</t>
         </is>
       </c>
-      <c r="J15" s="26" t="inlineStr">
+      <c r="J15" s="25" t="inlineStr">
         <is>
           <t>Stage 8</t>
         </is>
       </c>
-      <c r="K15" s="26" t="inlineStr">
+      <c r="K15" s="25" t="inlineStr">
         <is>
           <t>Strategist upbeat but evidence weak → weaker verdict wins until re-research</t>
         </is>
       </c>
-      <c r="L15" s="26" t="inlineStr">
+      <c r="L15" s="25" t="inlineStr">
         <is>
           <t>Company page → Brief, Intent</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="32" t="n">
+      <c r="A16" s="35" t="n">
         <v>8</v>
       </c>
-      <c r="B16" s="33" t="inlineStr">
+      <c r="B16" s="36" t="inlineStr">
         <is>
           <t>People</t>
         </is>
       </c>
-      <c r="C16" s="34" t="inlineStr">
+      <c r="C16" s="37" t="inlineStr">
         <is>
           <t>Buying group</t>
         </is>
       </c>
-      <c r="D16" s="33" t="inlineStr">
+      <c r="D16" s="36" t="inlineStr">
         <is>
           <t>Find people by the problem the account has, not by seniority.</t>
         </is>
       </c>
-      <c r="E16" s="26" t="inlineStr">
+      <c r="E16" s="25" t="inlineStr">
         <is>
           <t>twin.updated</t>
         </is>
       </c>
-      <c r="F16" s="26" t="inlineStr">
+      <c r="F16" s="25" t="inlineStr">
         <is>
           <t>Personas from the seller profile are matched to the problem; buying roles assigned (decision maker, champion, budget owner, influencer).</t>
         </is>
       </c>
-      <c r="G16" s="26" t="inlineStr">
+      <c r="G16" s="25" t="inlineStr">
         <is>
           <t>If ownership is unclear, no contacts are guessed.</t>
         </is>
       </c>
-      <c r="H16" s="31" t="inlineStr">
+      <c r="H16" s="27" t="inlineStr">
         <is>
           <t>System</t>
         </is>
       </c>
-      <c r="I16" s="26" t="inlineStr">
+      <c r="I16" s="25" t="inlineStr">
         <is>
           <t>Buying-group map and selected members</t>
         </is>
       </c>
-      <c r="J16" s="26" t="inlineStr">
+      <c r="J16" s="25" t="inlineStr">
         <is>
           <t>Stage 9</t>
         </is>
       </c>
-      <c r="K16" s="26" t="inlineStr">
+      <c r="K16" s="25" t="inlineStr">
         <is>
           <t>No owner found → stops; Coverage shows the gap</t>
         </is>
       </c>
-      <c r="L16" s="26" t="inlineStr">
+      <c r="L16" s="25" t="inlineStr">
         <is>
           <t>Coverage; People</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="32" t="n">
+      <c r="A17" s="35" t="n">
         <v>9</v>
       </c>
-      <c r="B17" s="33" t="inlineStr">
+      <c r="B17" s="36" t="inlineStr">
         <is>
           <t>People</t>
         </is>
       </c>
-      <c r="C17" s="34" t="inlineStr">
+      <c r="C17" s="37" t="inlineStr">
         <is>
           <t>Contact enrichment</t>
         </is>
       </c>
-      <c r="D17" s="33" t="inlineStr">
+      <c r="D17" s="36" t="inlineStr">
         <is>
           <t>Fill only missing data, and only for selected people.</t>
         </is>
       </c>
-      <c r="E17" s="26" t="inlineStr">
+      <c r="E17" s="25" t="inlineStr">
         <is>
           <t>buying_group.mapped</t>
         </is>
       </c>
-      <c r="F17" s="26" t="inlineStr">
+      <c r="F17" s="25" t="inlineStr">
         <is>
           <t>Paid lookups (Apollo, approval-gated) run only for required missing fields. Email checked with a free MX check. Suppression and lawful basis checked.</t>
         </is>
       </c>
-      <c r="G17" s="26" t="inlineStr">
+      <c r="G17" s="25" t="inlineStr">
         <is>
           <t>Within budget. Suppression and lawful basis are checked here and again before send.</t>
         </is>
       </c>
-      <c r="H17" s="31" t="inlineStr">
+      <c r="H17" s="27" t="inlineStr">
         <is>
           <t>System</t>
         </is>
       </c>
-      <c r="I17" s="26" t="inlineStr">
+      <c r="I17" s="25" t="inlineStr">
         <is>
           <t>Outreach-ready contacts</t>
         </is>
       </c>
-      <c r="J17" s="26" t="inlineStr">
+      <c r="J17" s="25" t="inlineStr">
         <is>
           <t>Stage 10</t>
         </is>
       </c>
-      <c r="K17" s="26" t="inlineStr">
+      <c r="K17" s="25" t="inlineStr">
         <is>
           <t>No usable email → LinkedIn (T1) or find an email</t>
         </is>
       </c>
-      <c r="L17" s="26" t="inlineStr">
+      <c r="L17" s="25" t="inlineStr">
         <is>
           <t>People</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="39" t="n">
+      <c r="A18" s="41" t="n">
         <v>10</v>
       </c>
-      <c r="B18" s="40" t="inlineStr">
+      <c r="B18" s="42" t="inlineStr">
         <is>
           <t>Outreach</t>
         </is>
       </c>
-      <c r="C18" s="41" t="inlineStr">
+      <c r="C18" s="43" t="inlineStr">
         <is>
           <t>Readiness</t>
         </is>
       </c>
-      <c r="D18" s="40" t="inlineStr">
+      <c r="D18" s="42" t="inlineStr">
         <is>
           <t>Stop weak intelligence from turning into outbound messages.</t>
         </is>
       </c>
-      <c r="E18" s="26" t="inlineStr">
+      <c r="E18" s="25" t="inlineStr">
         <is>
           <t>contacts.ready</t>
         </is>
       </c>
-      <c r="F18" s="26" t="inlineStr">
+      <c r="F18" s="25" t="inlineStr">
         <is>
           <t>Decision per person, in order: negative news → evidence strength → identity and lawful basis → suppression and deliverability → buying role.</t>
         </is>
       </c>
-      <c r="G18" s="26" t="inlineStr">
+      <c r="G18" s="25" t="inlineStr">
         <is>
           <t>Strong evidence = 1 verified trigger, or 2 independent reports, within 90 days, or a validated opportunity. Eligible roles: decision maker, champion.</t>
         </is>
       </c>
-      <c r="H18" s="31" t="inlineStr">
+      <c r="H18" s="27" t="inlineStr">
         <is>
           <t>System</t>
         </is>
       </c>
-      <c r="I18" s="26" t="inlineStr">
+      <c r="I18" s="25" t="inlineStr">
         <is>
           <t>Ready, research further, watch, human review or disqualified</t>
         </is>
       </c>
-      <c r="J18" s="26" t="inlineStr">
+      <c r="J18" s="25" t="inlineStr">
         <is>
           <t>Ready → stage 11</t>
         </is>
       </c>
-      <c r="K18" s="26" t="inlineStr">
+      <c r="K18" s="25" t="inlineStr">
         <is>
           <t>Weak → one targeted re-research, then watch 30 days. Negative news → watch 90 days or review. Identity/role issue → human review. Suppressed → disqualified.</t>
         </is>
       </c>
-      <c r="L18" s="26" t="inlineStr">
+      <c r="L18" s="25" t="inlineStr">
         <is>
           <t>Company page → Readiness; Approvals</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="39" t="n">
+      <c r="A19" s="41" t="n">
         <v>11</v>
       </c>
-      <c r="B19" s="40" t="inlineStr">
+      <c r="B19" s="42" t="inlineStr">
         <is>
           <t>Outreach</t>
         </is>
       </c>
-      <c r="C19" s="41" t="inlineStr">
+      <c r="C19" s="43" t="inlineStr">
         <is>
           <t>Draft and approve</t>
         </is>
       </c>
-      <c r="D19" s="40" t="inlineStr">
+      <c r="D19" s="42" t="inlineStr">
         <is>
           <t>Draft from the strongest relevant facts, then have a person approve.</t>
         </is>
       </c>
-      <c r="E19" s="26" t="inlineStr">
+      <c r="E19" s="25" t="inlineStr">
         <is>
           <t>readiness.decided</t>
         </is>
       </c>
-      <c r="F19" s="26" t="inlineStr">
+      <c r="F19" s="25" t="inlineStr">
         <is>
           <t>Writer uses the brief, cited facts and the knowledge base (playbook, persona, examples, case studies). Guardrails check facts, compliance (unsubscribe, address) and quality.</t>
         </is>
       </c>
-      <c r="G19" s="26" t="inlineStr">
+      <c r="G19" s="25" t="inlineStr">
         <is>
           <t>Every claim cites a usable, fresh fact. Three guardrail failures → a person. Tier sets the approval policy.</t>
         </is>
       </c>
-      <c r="H19" s="27" t="inlineStr">
+      <c r="H19" s="26" t="inlineStr">
         <is>
           <t>AI + human</t>
         </is>
       </c>
-      <c r="I19" s="26" t="inlineStr">
+      <c r="I19" s="25" t="inlineStr">
         <is>
           <t>Approved draft with cited evidence</t>
         </is>
       </c>
-      <c r="J19" s="26" t="inlineStr">
+      <c r="J19" s="25" t="inlineStr">
         <is>
           <t>Stage 12</t>
         </is>
       </c>
-      <c r="K19" s="26" t="inlineStr">
+      <c r="K19" s="25" t="inlineStr">
         <is>
           <t>Rejected or edited by a person; withdrawn if a cited fact is flagged wrong</t>
         </is>
       </c>
-      <c r="L19" s="26" t="inlineStr">
+      <c r="L19" s="25" t="inlineStr">
         <is>
           <t>Approvals; Emails</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="42" t="n">
+      <c r="A20" s="44" t="n">
         <v>12</v>
       </c>
-      <c r="B20" s="43" t="inlineStr">
+      <c r="B20" s="45" t="inlineStr">
         <is>
           <t>Engagement</t>
         </is>
       </c>
-      <c r="C20" s="44" t="inlineStr">
+      <c r="C20" s="46" t="inlineStr">
         <is>
           <t>Send and score</t>
         </is>
       </c>
-      <c r="D20" s="43" t="inlineStr">
+      <c r="D20" s="45" t="inlineStr">
         <is>
           <t>Send safely across channels, measure, and score at account level.</t>
         </is>
       </c>
-      <c r="E20" s="26" t="inlineStr">
+      <c r="E20" s="25" t="inlineStr">
         <is>
           <t>draft.approved, engagement events</t>
         </is>
       </c>
-      <c r="F20" s="26" t="inlineStr">
+      <c r="F20" s="25" t="inlineStr">
         <is>
           <t>Emails sent on schedule; LinkedIn tasks created; opens, clicks, replies, site and pricing visits recorded as signals; engagement score and buying stage updated; intent re-read.</t>
         </is>
       </c>
-      <c r="G20" s="26" t="inlineStr">
+      <c r="G20" s="25" t="inlineStr">
         <is>
           <t>40 per mailbox per day, 400 overall. Bounce breaker at 2% (after 50 sends). Send-once keys. Engagement halves every 14 days; anonymous activity counts 50%. Aware 10, Engaged 35, MQA 70.</t>
         </is>
       </c>
-      <c r="H20" s="31" t="inlineStr">
+      <c r="H20" s="27" t="inlineStr">
         <is>
           <t>System</t>
         </is>
       </c>
-      <c r="I20" s="26" t="inlineStr">
+      <c r="I20" s="25" t="inlineStr">
         <is>
           <t>Sends, signals, replies, buying stage</t>
         </is>
       </c>
-      <c r="J20" s="26" t="inlineStr">
+      <c r="J20" s="25" t="inlineStr">
         <is>
           <t>MQA or positive reply → stage 13</t>
         </is>
       </c>
-      <c r="K20" s="26" t="inlineStr">
+      <c r="K20" s="25" t="inlineStr">
         <is>
           <t>"Not now" reply → watch 60 days; watched account turning hot → research restarts</t>
         </is>
       </c>
-      <c r="L20" s="26" t="inlineStr">
+      <c r="L20" s="25" t="inlineStr">
         <is>
           <t>Signals; Emails; Today</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="42" t="n">
+      <c r="A21" s="44" t="n">
         <v>13</v>
       </c>
-      <c r="B21" s="43" t="inlineStr">
+      <c r="B21" s="45" t="inlineStr">
         <is>
           <t>Engagement</t>
         </is>
       </c>
-      <c r="C21" s="44" t="inlineStr">
+      <c r="C21" s="46" t="inlineStr">
         <is>
           <t>Hand-off and learning</t>
         </is>
       </c>
-      <c r="D21" s="43" t="inlineStr">
+      <c r="D21" s="45" t="inlineStr">
         <is>
           <t>Give a rep a fact-checked briefing when the account engages, then learn from the outcome.</t>
         </is>
       </c>
-      <c r="E21" s="26" t="inlineStr">
+      <c r="E21" s="25" t="inlineStr">
         <is>
           <t>MQA, positive reply, manual, deal closed</t>
         </is>
       </c>
-      <c r="F21" s="26" t="inlineStr">
+      <c r="F21" s="25" t="inlineStr">
         <is>
           <t>Hand-off created with the brief and evidence; automation pauses for the whole account; owner asked to acknowledge. Positive-reply emails are saved to the knowledge base.</t>
         </is>
       </c>
-      <c r="G21" s="26" t="inlineStr">
+      <c r="G21" s="25" t="inlineStr">
         <is>
           <t>Acknowledge within 24 hours (overdue escalates). Lost deals return via the watchlist after 90 days. Weights retune only after 200 closed deals.</t>
         </is>
       </c>
-      <c r="H21" s="27" t="inlineStr">
+      <c r="H21" s="26" t="inlineStr">
         <is>
           <t>System + human</t>
         </is>
       </c>
-      <c r="I21" s="26" t="inlineStr">
+      <c r="I21" s="25" t="inlineStr">
         <is>
           <t>Alert, briefing, outcome record</t>
         </is>
       </c>
-      <c r="J21" s="26" t="inlineStr">
+      <c r="J21" s="25" t="inlineStr">
         <is>
           <t>Opportunity in CRM → won or lost</t>
         </is>
       </c>
-      <c r="K21" s="26" t="inlineStr">
+      <c r="K21" s="25" t="inlineStr">
         <is>
           <t>Lost → watchlist 90 days</t>
         </is>
       </c>
-      <c r="L21" s="26" t="inlineStr">
+      <c r="L21" s="25" t="inlineStr">
         <is>
           <t>Hand-offs; Opportunities</t>
         </is>
@@ -2608,7 +3551,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2672,602 +3615,602 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Exclusion: existing relationship</t>
         </is>
       </c>
-      <c r="B5" s="26" t="n">
+      <c r="B5" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="26" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t>Account is a customer or has an open opportunity</t>
         </is>
       </c>
-      <c r="D5" s="26" t="inlineStr">
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E5" s="26" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t>Set to Customer / Opportunity; sales owns it; run stops</t>
         </is>
       </c>
-      <c r="F5" s="26" t="inlineStr">
+      <c r="F5" s="25" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>Exclusion: do-not-contact</t>
         </is>
       </c>
-      <c r="B6" s="26" t="n">
+      <c r="B6" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="26" t="inlineStr">
+      <c r="C6" s="25" t="inlineStr">
         <is>
           <t>Account flagged do-not-contact</t>
         </is>
       </c>
-      <c r="D6" s="26" t="inlineStr">
+      <c r="D6" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E6" s="26" t="inlineStr">
+      <c r="E6" s="25" t="inlineStr">
         <is>
           <t>Disqualified at once (compliance)</t>
         </is>
       </c>
-      <c r="F6" s="26" t="inlineStr">
+      <c r="F6" s="25" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>Exclusion: recent lost deal</t>
         </is>
       </c>
-      <c r="B7" s="26" t="n">
+      <c r="B7" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="26" t="inlineStr">
+      <c r="C7" s="25" t="inlineStr">
         <is>
           <t>Deal lost within the last 90 days</t>
         </is>
       </c>
-      <c r="D7" s="26" t="inlineStr">
+      <c r="D7" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E7" s="26" t="inlineStr">
+      <c r="E7" s="25" t="inlineStr">
         <is>
           <t>Watchlist until the 90-day cooldown ends</t>
         </is>
       </c>
-      <c r="F7" s="26" t="inlineStr">
+      <c r="F7" s="25" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="26" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>Hard targeting rule</t>
         </is>
       </c>
-      <c r="B8" s="26" t="n">
+      <c r="B8" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="C8" s="26" t="inlineStr">
+      <c r="C8" s="25" t="inlineStr">
         <is>
           <t>Country and minimum size (Manch: India, more than 5,000 employees)</t>
         </is>
       </c>
-      <c r="D8" s="26" t="inlineStr">
+      <c r="D8" s="25" t="inlineStr">
         <is>
           <t>Continue</t>
         </is>
       </c>
-      <c r="E8" s="26" t="inlineStr">
+      <c r="E8" s="25" t="inlineStr">
         <is>
           <t>Outside → proposed rejection. Unknown → run stops and asks for the data in the next upload</t>
         </is>
       </c>
-      <c r="F8" s="26" t="inlineStr">
+      <c r="F8" s="25" t="inlineStr">
         <is>
           <t>Per client</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="26" t="inlineStr">
+      <c r="A9" s="25" t="inlineStr">
         <is>
           <t>Fit floor</t>
         </is>
       </c>
-      <c r="B9" s="26" t="n">
+      <c r="B9" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="C9" s="26" t="inlineStr">
+      <c r="C9" s="25" t="inlineStr">
         <is>
           <t>Fit ≥ 40 (unknown fit passes; research decides)</t>
         </is>
       </c>
-      <c r="D9" s="26" t="inlineStr">
+      <c r="D9" s="25" t="inlineStr">
         <is>
           <t>Continue</t>
         </is>
       </c>
-      <c r="E9" s="26" t="inlineStr">
+      <c r="E9" s="25" t="inlineStr">
         <is>
           <t>Proposed rejection; a person confirms or overrides</t>
         </is>
       </c>
-      <c r="F9" s="26" t="inlineStr">
+      <c r="F9" s="25" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="26" t="inlineStr">
+      <c r="A10" s="25" t="inlineStr">
         <is>
           <t>Identity conflict</t>
         </is>
       </c>
-      <c r="B10" s="26" t="n">
+      <c r="B10" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="C10" s="26" t="inlineStr">
+      <c r="C10" s="25" t="inlineStr">
         <is>
           <t>Person's fields agree across sources</t>
         </is>
       </c>
-      <c r="D10" s="26" t="inlineStr">
+      <c r="D10" s="25" t="inlineStr">
         <is>
           <t>Continue</t>
         </is>
       </c>
-      <c r="E10" s="26" t="inlineStr">
+      <c r="E10" s="25" t="inlineStr">
         <is>
           <t>One focused re-check; still conflicting → human review</t>
         </is>
       </c>
-      <c r="F10" s="26" t="inlineStr">
+      <c r="F10" s="25" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="26" t="inlineStr">
+      <c r="A11" s="25" t="inlineStr">
         <is>
           <t>Research budget</t>
         </is>
       </c>
-      <c r="B11" s="26" t="inlineStr">
+      <c r="B11" s="25" t="inlineStr">
         <is>
           <t>5–6</t>
         </is>
       </c>
-      <c r="C11" s="26" t="inlineStr">
+      <c r="C11" s="25" t="inlineStr">
         <is>
           <t>Spend within tier budget (T1 $5, T2 $2, T3 $0.75) and the client's monthly cap</t>
         </is>
       </c>
-      <c r="D11" s="26" t="inlineStr">
+      <c r="D11" s="25" t="inlineStr">
         <is>
           <t>Continue</t>
         </is>
       </c>
-      <c r="E11" s="26" t="inlineStr">
+      <c r="E11" s="25" t="inlineStr">
         <is>
           <t>Research stops with reason; monthly cap warns at 80%</t>
         </is>
       </c>
-      <c r="F11" s="26" t="inlineStr">
+      <c r="F11" s="25" t="inlineStr">
         <is>
           <t>Fixed (monthly cap per client)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="26" t="inlineStr">
+      <c r="A12" s="25" t="inlineStr">
         <is>
           <t>Hot intent upgrade</t>
         </is>
       </c>
-      <c r="B12" s="26" t="n">
+      <c r="B12" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="C12" s="26" t="inlineStr">
+      <c r="C12" s="25" t="inlineStr">
         <is>
           <t>Intent ≥ 65 with 2+ independent families</t>
         </is>
       </c>
-      <c r="D12" s="26" t="inlineStr">
+      <c r="D12" s="25" t="inlineStr">
         <is>
           <t>Tier → T1 and deep dive now</t>
         </is>
       </c>
-      <c r="E12" s="26" t="inlineStr">
+      <c r="E12" s="25" t="inlineStr">
         <is>
           <t>Tier unchanged</t>
         </is>
       </c>
-      <c r="F12" s="26" t="inlineStr">
+      <c r="F12" s="25" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="26" t="inlineStr">
+      <c r="A13" s="25" t="inlineStr">
         <is>
           <t>Buying-group ownership</t>
         </is>
       </c>
-      <c r="B13" s="26" t="n">
+      <c r="B13" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="C13" s="26" t="inlineStr">
+      <c r="C13" s="25" t="inlineStr">
         <is>
           <t>A clear owner of the problem is identified</t>
         </is>
       </c>
-      <c r="D13" s="26" t="inlineStr">
+      <c r="D13" s="25" t="inlineStr">
         <is>
           <t>Continue</t>
         </is>
       </c>
-      <c r="E13" s="26" t="inlineStr">
+      <c r="E13" s="25" t="inlineStr">
         <is>
           <t>No contacts guessed; stops</t>
         </is>
       </c>
-      <c r="F13" s="26" t="inlineStr">
+      <c r="F13" s="25" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="26" t="inlineStr">
+      <c r="A14" s="25" t="inlineStr">
         <is>
           <t>Negative evidence</t>
         </is>
       </c>
-      <c r="B14" s="26" t="n">
+      <c r="B14" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="C14" s="26" t="inlineStr">
+      <c r="C14" s="25" t="inlineStr">
         <is>
           <t>No confirmed blocker (acquired, bankrupt, signed a competitor)</t>
         </is>
       </c>
-      <c r="D14" s="26" t="inlineStr">
+      <c r="D14" s="25" t="inlineStr">
         <is>
           <t>Continue</t>
         </is>
       </c>
-      <c r="E14" s="26" t="inlineStr">
+      <c r="E14" s="25" t="inlineStr">
         <is>
           <t>Confirmed → disqualified. Possible → human review. Unconfirmed → watch 90 days</t>
         </is>
       </c>
-      <c r="F14" s="26" t="inlineStr">
+      <c r="F14" s="25" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="26" t="inlineStr">
+      <c r="A15" s="25" t="inlineStr">
         <is>
           <t>Evidence strength</t>
         </is>
       </c>
-      <c r="B15" s="26" t="n">
+      <c r="B15" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="C15" s="26" t="inlineStr">
+      <c r="C15" s="25" t="inlineStr">
         <is>
           <t>1 verified trigger, or 2 independent reports, in 90 days, or a validated opportunity</t>
         </is>
       </c>
-      <c r="D15" s="26" t="inlineStr">
+      <c r="D15" s="25" t="inlineStr">
         <is>
           <t>Continue</t>
         </is>
       </c>
-      <c r="E15" s="26" t="inlineStr">
+      <c r="E15" s="25" t="inlineStr">
         <is>
           <t>First time → one targeted re-research. After that → watch 30 days</t>
         </is>
       </c>
-      <c r="F15" s="26" t="inlineStr">
+      <c r="F15" s="25" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="26" t="inlineStr">
+      <c r="A16" s="25" t="inlineStr">
         <is>
           <t>Identity and lawful basis</t>
         </is>
       </c>
-      <c r="B16" s="26" t="n">
+      <c r="B16" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="C16" s="26" t="inlineStr">
+      <c r="C16" s="25" t="inlineStr">
         <is>
           <t>Email, title and company verified or probable; lawful basis for the region</t>
         </is>
       </c>
-      <c r="D16" s="26" t="inlineStr">
+      <c r="D16" s="25" t="inlineStr">
         <is>
           <t>Continue</t>
         </is>
       </c>
-      <c r="E16" s="26" t="inlineStr">
+      <c r="E16" s="25" t="inlineStr">
         <is>
           <t>Human review with the exact reason</t>
         </is>
       </c>
-      <c r="F16" s="26" t="inlineStr">
+      <c r="F16" s="25" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="26" t="inlineStr">
+      <c r="A17" s="25" t="inlineStr">
         <is>
           <t>Suppression and deliverability</t>
         </is>
       </c>
-      <c r="B17" s="26" t="n">
+      <c r="B17" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="C17" s="26" t="inlineStr">
+      <c r="C17" s="25" t="inlineStr">
         <is>
           <t>Not suppressed; email deliverable (MX check)</t>
         </is>
       </c>
-      <c r="D17" s="26" t="inlineStr">
+      <c r="D17" s="25" t="inlineStr">
         <is>
           <t>Continue</t>
         </is>
       </c>
-      <c r="E17" s="26" t="inlineStr">
+      <c r="E17" s="25" t="inlineStr">
         <is>
           <t>Suppressed → disqualified. Undeliverable → human review</t>
         </is>
       </c>
-      <c r="F17" s="26" t="inlineStr">
+      <c r="F17" s="25" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="26" t="inlineStr">
+      <c r="A18" s="25" t="inlineStr">
         <is>
           <t>Buying role</t>
         </is>
       </c>
-      <c r="B18" s="26" t="n">
+      <c r="B18" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="C18" s="26" t="inlineStr">
+      <c r="C18" s="25" t="inlineStr">
         <is>
           <t>Decision maker or champion</t>
         </is>
       </c>
-      <c r="D18" s="26" t="inlineStr">
+      <c r="D18" s="25" t="inlineStr">
         <is>
           <t>Ready</t>
         </is>
       </c>
-      <c r="E18" s="26" t="inlineStr">
+      <c r="E18" s="25" t="inlineStr">
         <is>
           <t>Human review</t>
         </is>
       </c>
-      <c r="F18" s="26" t="inlineStr">
+      <c r="F18" s="25" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="26" t="inlineStr">
+      <c r="A19" s="25" t="inlineStr">
         <is>
           <t>Fact guardrail</t>
         </is>
       </c>
-      <c r="B19" s="26" t="n">
+      <c r="B19" s="25" t="n">
         <v>11</v>
       </c>
-      <c r="C19" s="26" t="inlineStr">
+      <c r="C19" s="25" t="inlineStr">
         <is>
           <t>Every claim cites a verified or probable, fresh fact</t>
         </is>
       </c>
-      <c r="D19" s="26" t="inlineStr">
+      <c r="D19" s="25" t="inlineStr">
         <is>
           <t>Continue</t>
         </is>
       </c>
-      <c r="E19" s="26" t="inlineStr">
+      <c r="E19" s="25" t="inlineStr">
         <is>
           <t>Redraft; 3 failures → a person</t>
         </is>
       </c>
-      <c r="F19" s="26" t="inlineStr">
+      <c r="F19" s="25" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="26" t="inlineStr">
+      <c r="A20" s="25" t="inlineStr">
         <is>
           <t>Compliance guardrail</t>
         </is>
       </c>
-      <c r="B20" s="26" t="n">
+      <c r="B20" s="25" t="n">
         <v>11</v>
       </c>
-      <c r="C20" s="26" t="inlineStr">
+      <c r="C20" s="25" t="inlineStr">
         <is>
           <t>Unsubscribe line and sender address present</t>
         </is>
       </c>
-      <c r="D20" s="26" t="inlineStr">
+      <c r="D20" s="25" t="inlineStr">
         <is>
           <t>Continue</t>
         </is>
       </c>
-      <c r="E20" s="26" t="inlineStr">
+      <c r="E20" s="25" t="inlineStr">
         <is>
           <t>Redraft; 3 failures → a person</t>
         </is>
       </c>
-      <c r="F20" s="26" t="inlineStr">
+      <c r="F20" s="25" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="26" t="inlineStr">
+      <c r="A21" s="25" t="inlineStr">
         <is>
           <t>Human approval</t>
         </is>
       </c>
-      <c r="B21" s="26" t="n">
+      <c r="B21" s="25" t="n">
         <v>11</v>
       </c>
-      <c r="C21" s="26" t="inlineStr">
+      <c r="C21" s="25" t="inlineStr">
         <is>
           <t>A person approves the draft</t>
         </is>
       </c>
-      <c r="D21" s="26" t="inlineStr">
+      <c r="D21" s="25" t="inlineStr">
         <is>
           <t>Queued to send</t>
         </is>
       </c>
-      <c r="E21" s="26" t="inlineStr">
+      <c r="E21" s="25" t="inlineStr">
         <is>
           <t>Edited, rejected or left waiting</t>
         </is>
       </c>
-      <c r="F21" s="26" t="inlineStr">
+      <c r="F21" s="25" t="inlineStr">
         <is>
           <t>Fixed (policy by tier)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="26" t="inlineStr">
+      <c r="A22" s="25" t="inlineStr">
         <is>
           <t>Sending safety</t>
         </is>
       </c>
-      <c r="B22" s="26" t="n">
+      <c r="B22" s="25" t="n">
         <v>12</v>
       </c>
-      <c r="C22" s="26" t="inlineStr">
+      <c r="C22" s="25" t="inlineStr">
         <is>
           <t>Under mailbox (40/day) and global (400/day) caps; bounce rate under 2%</t>
         </is>
       </c>
-      <c r="D22" s="26" t="inlineStr">
+      <c r="D22" s="25" t="inlineStr">
         <is>
           <t>Send</t>
         </is>
       </c>
-      <c r="E22" s="26" t="inlineStr">
+      <c r="E22" s="25" t="inlineStr">
         <is>
           <t>Held to the next day; bounce breaker pauses the mailbox</t>
         </is>
       </c>
-      <c r="F22" s="26" t="inlineStr">
+      <c r="F22" s="25" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="26" t="inlineStr">
+      <c r="A23" s="25" t="inlineStr">
         <is>
           <t>MQA threshold</t>
         </is>
       </c>
-      <c r="B23" s="26" t="n">
+      <c r="B23" s="25" t="n">
         <v>12</v>
       </c>
-      <c r="C23" s="26" t="inlineStr">
+      <c r="C23" s="25" t="inlineStr">
         <is>
           <t>Account engagement ≥ 70</t>
         </is>
       </c>
-      <c r="D23" s="26" t="inlineStr">
+      <c r="D23" s="25" t="inlineStr">
         <is>
           <t>Hand-off to sales</t>
         </is>
       </c>
-      <c r="E23" s="26" t="inlineStr">
+      <c r="E23" s="25" t="inlineStr">
         <is>
           <t>Stays in sequence</t>
         </is>
       </c>
-      <c r="F23" s="26" t="inlineStr">
+      <c r="F23" s="25" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="26" t="inlineStr">
+      <c r="A24" s="25" t="inlineStr">
         <is>
           <t>Positive reply</t>
         </is>
       </c>
-      <c r="B24" s="26" t="n">
+      <c r="B24" s="25" t="n">
         <v>12</v>
       </c>
-      <c r="C24" s="26" t="inlineStr">
+      <c r="C24" s="25" t="inlineStr">
         <is>
           <t>A reply classified positive</t>
         </is>
       </c>
-      <c r="D24" s="26" t="inlineStr">
+      <c r="D24" s="25" t="inlineStr">
         <is>
           <t>Hand-off at once</t>
         </is>
       </c>
-      <c r="E24" s="26" t="inlineStr">
+      <c r="E24" s="25" t="inlineStr">
         <is>
           <t>Neutral → continue; not now → watch 60 days; negative → stop</t>
         </is>
       </c>
-      <c r="F24" s="26" t="inlineStr">
+      <c r="F24" s="25" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -3283,7 +4226,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3341,540 +4284,540 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Pipeline status</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>queued</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t>Waiting for the background queue</t>
         </is>
       </c>
-      <c r="D5" s="26" t="inlineStr">
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>Import, re-research, watchlist re-check, cut-off run recovered</t>
         </is>
       </c>
-      <c r="E5" s="26" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t>A worker picks it up → running</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>Pipeline status</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>running</t>
         </is>
       </c>
-      <c r="C6" s="26" t="inlineStr">
+      <c r="C6" s="25" t="inlineStr">
         <is>
           <t>A stage is being worked on now</t>
         </is>
       </c>
-      <c r="D6" s="26" t="inlineStr">
+      <c r="D6" s="25" t="inlineStr">
         <is>
           <t>Worker starts the run</t>
         </is>
       </c>
-      <c r="E6" s="26" t="inlineStr">
+      <c r="E6" s="25" t="inlineStr">
         <is>
           <t>done, blocked, idle or error. No activity for 10 minutes → put back in the queue</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>Pipeline status</t>
         </is>
       </c>
-      <c r="B7" s="26" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>blocked</t>
         </is>
       </c>
-      <c r="C7" s="26" t="inlineStr">
+      <c r="C7" s="25" t="inlineStr">
         <is>
           <t>Waiting on a check or a person</t>
         </is>
       </c>
-      <c r="D7" s="26" t="inlineStr">
+      <c r="D7" s="25" t="inlineStr">
         <is>
           <t>A gate needs a human, or no ready contacts</t>
         </is>
       </c>
-      <c r="E7" s="26" t="inlineStr">
+      <c r="E7" s="25" t="inlineStr">
         <is>
           <t>Person acts, or new data arrives</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="26" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>Pipeline status</t>
         </is>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>idle</t>
         </is>
       </c>
-      <c r="C8" s="26" t="inlineStr">
+      <c r="C8" s="25" t="inlineStr">
         <is>
           <t>Paused; nothing to do now</t>
         </is>
       </c>
-      <c r="D8" s="26" t="inlineStr">
+      <c r="D8" s="25" t="inlineStr">
         <is>
           <t>Run finished without outreach (e.g. no ready contacts)</t>
         </is>
       </c>
-      <c r="E8" s="26" t="inlineStr">
+      <c r="E8" s="25" t="inlineStr">
         <is>
           <t>New data, re-research or watchlist re-check</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="26" t="inlineStr">
+      <c r="A9" s="25" t="inlineStr">
         <is>
           <t>Pipeline status</t>
         </is>
       </c>
-      <c r="B9" s="26" t="inlineStr">
+      <c r="B9" s="25" t="inlineStr">
         <is>
           <t>done</t>
         </is>
       </c>
-      <c r="C9" s="26" t="inlineStr">
+      <c r="C9" s="25" t="inlineStr">
         <is>
           <t>All stages complete</t>
         </is>
       </c>
-      <c r="D9" s="26" t="inlineStr">
+      <c r="D9" s="25" t="inlineStr">
         <is>
           <t>Run reached the end</t>
         </is>
       </c>
-      <c r="E9" s="26" t="inlineStr">
+      <c r="E9" s="25" t="inlineStr">
         <is>
           <t>New import or re-research</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="26" t="inlineStr">
+      <c r="A10" s="25" t="inlineStr">
         <is>
           <t>Pipeline status</t>
         </is>
       </c>
-      <c r="B10" s="26" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="C10" s="26" t="inlineStr">
+      <c r="C10" s="25" t="inlineStr">
         <is>
           <t>Needs attention</t>
         </is>
       </c>
-      <c r="D10" s="26" t="inlineStr">
+      <c r="D10" s="25" t="inlineStr">
         <is>
           <t>Unexpected failure (retried first)</t>
         </is>
       </c>
-      <c r="E10" s="26" t="inlineStr">
+      <c r="E10" s="25" t="inlineStr">
         <is>
           <t>Fixed and re-run</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="26" t="inlineStr">
+      <c r="A11" s="25" t="inlineStr">
         <is>
           <t>Buying stage</t>
         </is>
       </c>
-      <c r="B11" s="26" t="inlineStr">
+      <c r="B11" s="25" t="inlineStr">
         <is>
           <t>UNAWARE</t>
         </is>
       </c>
-      <c r="C11" s="26" t="inlineStr">
+      <c r="C11" s="25" t="inlineStr">
         <is>
           <t>No meaningful engagement</t>
         </is>
       </c>
-      <c r="D11" s="26" t="inlineStr">
+      <c r="D11" s="25" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="E11" s="26" t="inlineStr">
+      <c r="E11" s="25" t="inlineStr">
         <is>
           <t>Engagement ≥ 10 → AWARE</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="26" t="inlineStr">
+      <c r="A12" s="25" t="inlineStr">
         <is>
           <t>Buying stage</t>
         </is>
       </c>
-      <c r="B12" s="26" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>AWARE</t>
         </is>
       </c>
-      <c r="C12" s="26" t="inlineStr">
+      <c r="C12" s="25" t="inlineStr">
         <is>
           <t>Some engagement</t>
         </is>
       </c>
-      <c r="D12" s="26" t="inlineStr">
+      <c r="D12" s="25" t="inlineStr">
         <is>
           <t>Engagement ≥ 10</t>
         </is>
       </c>
-      <c r="E12" s="26" t="inlineStr">
+      <c r="E12" s="25" t="inlineStr">
         <is>
           <t>≥ 35 → ENGAGED</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="26" t="inlineStr">
+      <c r="A13" s="25" t="inlineStr">
         <is>
           <t>Buying stage</t>
         </is>
       </c>
-      <c r="B13" s="26" t="inlineStr">
+      <c r="B13" s="25" t="inlineStr">
         <is>
           <t>ENGAGED</t>
         </is>
       </c>
-      <c r="C13" s="26" t="inlineStr">
+      <c r="C13" s="25" t="inlineStr">
         <is>
           <t>Clear engagement</t>
         </is>
       </c>
-      <c r="D13" s="26" t="inlineStr">
+      <c r="D13" s="25" t="inlineStr">
         <is>
           <t>Engagement ≥ 35</t>
         </is>
       </c>
-      <c r="E13" s="26" t="inlineStr">
+      <c r="E13" s="25" t="inlineStr">
         <is>
           <t>≥ 70 → MQA</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="26" t="inlineStr">
+      <c r="A14" s="25" t="inlineStr">
         <is>
           <t>Buying stage</t>
         </is>
       </c>
-      <c r="B14" s="26" t="inlineStr">
+      <c r="B14" s="25" t="inlineStr">
         <is>
           <t>MQA</t>
         </is>
       </c>
-      <c r="C14" s="26" t="inlineStr">
+      <c r="C14" s="25" t="inlineStr">
         <is>
           <t>Marketing-qualified account</t>
         </is>
       </c>
-      <c r="D14" s="26" t="inlineStr">
+      <c r="D14" s="25" t="inlineStr">
         <is>
           <t>Engagement ≥ 70</t>
         </is>
       </c>
-      <c r="E14" s="26" t="inlineStr">
+      <c r="E14" s="25" t="inlineStr">
         <is>
           <t>Hand-off created → OPPORTUNITY when sales opens a deal</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="26" t="inlineStr">
+      <c r="A15" s="25" t="inlineStr">
         <is>
           <t>Buying stage</t>
         </is>
       </c>
-      <c r="B15" s="26" t="inlineStr">
+      <c r="B15" s="25" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
-      <c r="C15" s="26" t="inlineStr">
+      <c r="C15" s="25" t="inlineStr">
         <is>
           <t>Parked until a re-check date</t>
         </is>
       </c>
-      <c r="D15" s="26" t="inlineStr">
+      <c r="D15" s="25" t="inlineStr">
         <is>
           <t>Weak evidence (30 d), negative news (90 d), lost deal (90 d), "not now" (60 d)</t>
         </is>
       </c>
-      <c r="E15" s="26" t="inlineStr">
+      <c r="E15" s="25" t="inlineStr">
         <is>
           <t>Re-check date, or intent turns hot, or engagement ≥ 35</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="26" t="inlineStr">
+      <c r="A16" s="25" t="inlineStr">
         <is>
           <t>Buying stage</t>
         </is>
       </c>
-      <c r="B16" s="26" t="inlineStr">
+      <c r="B16" s="25" t="inlineStr">
         <is>
           <t>RECYCLED</t>
         </is>
       </c>
-      <c r="C16" s="26" t="inlineStr">
+      <c r="C16" s="25" t="inlineStr">
         <is>
           <t>Returned after a closed or stalled cycle</t>
         </is>
       </c>
-      <c r="D16" s="26" t="inlineStr">
+      <c r="D16" s="25" t="inlineStr">
         <is>
           <t>Outcome recorded</t>
         </is>
       </c>
-      <c r="E16" s="26" t="inlineStr">
+      <c r="E16" s="25" t="inlineStr">
         <is>
           <t>Engagement ≥ 35 or new trigger</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="26" t="inlineStr">
+      <c r="A17" s="25" t="inlineStr">
         <is>
           <t>Buying stage</t>
         </is>
       </c>
-      <c r="B17" s="26" t="inlineStr">
+      <c r="B17" s="25" t="inlineStr">
         <is>
           <t>OPPORTUNITY</t>
         </is>
       </c>
-      <c r="C17" s="26" t="inlineStr">
+      <c r="C17" s="25" t="inlineStr">
         <is>
           <t>Sales is working a deal</t>
         </is>
       </c>
-      <c r="D17" s="26" t="inlineStr">
+      <c r="D17" s="25" t="inlineStr">
         <is>
           <t>CRM opportunity opened</t>
         </is>
       </c>
-      <c r="E17" s="26" t="inlineStr">
+      <c r="E17" s="25" t="inlineStr">
         <is>
           <t>Won → CUSTOMER; lost → watchlist</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="26" t="inlineStr">
+      <c r="A18" s="25" t="inlineStr">
         <is>
           <t>Buying stage</t>
         </is>
       </c>
-      <c r="B18" s="26" t="inlineStr">
+      <c r="B18" s="25" t="inlineStr">
         <is>
           <t>CUSTOMER</t>
         </is>
       </c>
-      <c r="C18" s="26" t="inlineStr">
+      <c r="C18" s="25" t="inlineStr">
         <is>
           <t>Existing customer</t>
         </is>
       </c>
-      <c r="D18" s="26" t="inlineStr">
+      <c r="D18" s="25" t="inlineStr">
         <is>
           <t>Deal won or CRM</t>
         </is>
       </c>
-      <c r="E18" s="26" t="inlineStr">
+      <c r="E18" s="25" t="inlineStr">
         <is>
           <t>Terminal (excluded from outreach)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="26" t="inlineStr">
+      <c r="A19" s="25" t="inlineStr">
         <is>
           <t>Buying stage</t>
         </is>
       </c>
-      <c r="B19" s="26" t="inlineStr">
+      <c r="B19" s="25" t="inlineStr">
         <is>
           <t>DISQUALIFIED</t>
         </is>
       </c>
-      <c r="C19" s="26" t="inlineStr">
+      <c r="C19" s="25" t="inlineStr">
         <is>
           <t>Ruled out</t>
         </is>
       </c>
-      <c r="D19" s="26" t="inlineStr">
+      <c r="D19" s="25" t="inlineStr">
         <is>
           <t>Confirmed rejection, do-not-contact, confirmed blocker</t>
         </is>
       </c>
-      <c r="E19" s="26" t="inlineStr">
+      <c r="E19" s="25" t="inlineStr">
         <is>
           <t>Person reverses it, or newer data meets the targeting rule</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="26" t="inlineStr">
+      <c r="A20" s="25" t="inlineStr">
         <is>
           <t>Readiness outcome</t>
         </is>
       </c>
-      <c r="B20" s="26" t="inlineStr">
+      <c r="B20" s="25" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
       </c>
-      <c r="C20" s="26" t="inlineStr">
+      <c r="C20" s="25" t="inlineStr">
         <is>
           <t>Contact may be drafted to</t>
         </is>
       </c>
-      <c r="D20" s="26" t="inlineStr">
+      <c r="D20" s="25" t="inlineStr">
         <is>
           <t>All readiness rules pass</t>
         </is>
       </c>
-      <c r="E20" s="26" t="inlineStr">
+      <c r="E20" s="25" t="inlineStr">
         <is>
           <t>Stage 11</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="26" t="inlineStr">
+      <c r="A21" s="25" t="inlineStr">
         <is>
           <t>Readiness outcome</t>
         </is>
       </c>
-      <c r="B21" s="26" t="inlineStr">
+      <c r="B21" s="25" t="inlineStr">
         <is>
           <t>targeted_re_research</t>
         </is>
       </c>
-      <c r="C21" s="26" t="inlineStr">
+      <c r="C21" s="25" t="inlineStr">
         <is>
           <t>One more focused research pass</t>
         </is>
       </c>
-      <c r="D21" s="26" t="inlineStr">
+      <c r="D21" s="25" t="inlineStr">
         <is>
           <t>Evidence weak, follow-up unused</t>
         </is>
       </c>
-      <c r="E21" s="26" t="inlineStr">
+      <c r="E21" s="25" t="inlineStr">
         <is>
           <t>Decide again</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="26" t="inlineStr">
+      <c r="A22" s="25" t="inlineStr">
         <is>
           <t>Readiness outcome</t>
         </is>
       </c>
-      <c r="B22" s="26" t="inlineStr">
+      <c r="B22" s="25" t="inlineStr">
         <is>
           <t>watch</t>
         </is>
       </c>
-      <c r="C22" s="26" t="inlineStr">
+      <c r="C22" s="25" t="inlineStr">
         <is>
           <t>Park and re-check later</t>
         </is>
       </c>
-      <c r="D22" s="26" t="inlineStr">
+      <c r="D22" s="25" t="inlineStr">
         <is>
           <t>Weak after follow-up; negative news</t>
         </is>
       </c>
-      <c r="E22" s="26" t="inlineStr">
+      <c r="E22" s="25" t="inlineStr">
         <is>
           <t>Re-check date</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="26" t="inlineStr">
+      <c r="A23" s="25" t="inlineStr">
         <is>
           <t>Readiness outcome</t>
         </is>
       </c>
-      <c r="B23" s="26" t="inlineStr">
+      <c r="B23" s="25" t="inlineStr">
         <is>
           <t>human_review</t>
         </is>
       </c>
-      <c r="C23" s="26" t="inlineStr">
+      <c r="C23" s="25" t="inlineStr">
         <is>
           <t>A person decides</t>
         </is>
       </c>
-      <c r="D23" s="26" t="inlineStr">
+      <c r="D23" s="25" t="inlineStr">
         <is>
           <t>Identity, lawful basis, deliverability, role or possible blocker</t>
         </is>
       </c>
-      <c r="E23" s="26" t="inlineStr">
+      <c r="E23" s="25" t="inlineStr">
         <is>
           <t>Person approves or rejects</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="26" t="inlineStr">
+      <c r="A24" s="25" t="inlineStr">
         <is>
           <t>Readiness outcome</t>
         </is>
       </c>
-      <c r="B24" s="26" t="inlineStr">
+      <c r="B24" s="25" t="inlineStr">
         <is>
           <t>disqualified</t>
         </is>
       </c>
-      <c r="C24" s="26" t="inlineStr">
+      <c r="C24" s="25" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="D24" s="26" t="inlineStr">
+      <c r="D24" s="25" t="inlineStr">
         <is>
           <t>Confirmed blocker or suppressed</t>
         </is>
       </c>
-      <c r="E24" s="26" t="inlineStr">
+      <c r="E24" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3890,7 +4833,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3966,294 +4909,294 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="45" t="inlineStr">
+      <c r="A5" s="47" t="inlineStr">
         <is>
           <t>Fit</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>Does the company match the client's ideal customer profile?</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t>0–100</t>
         </is>
       </c>
-      <c r="D5" s="26" t="inlineStr">
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>round(points earned ÷ max points of known components × 100)</t>
         </is>
       </c>
-      <c r="E5" s="26" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t>Industry (35; not scored in "any industry" mode), size (25: sweet spot 100%, mid 72%, minimum 32%), geography (15: primary 100%, secondary 67%, other 20%), tech stack (10: ERP +6, incumbent +3, workflow +1), partner network (15; configured, not scored yet)</t>
         </is>
       </c>
-      <c r="F5" s="26" t="inlineStr">
+      <c r="F5" s="25" t="inlineStr">
         <is>
           <t>Floor 40. Tier by fit: T1 ≥ 80, T2 ≥ 60</t>
         </is>
       </c>
-      <c r="G5" s="31" t="inlineStr">
+      <c r="G5" s="27" t="inlineStr">
         <is>
           <t>System</t>
         </is>
       </c>
-      <c r="H5" s="26" t="inlineStr">
+      <c r="H5" s="25" t="inlineStr">
         <is>
           <t>Weights and settings per client; ratios fixed</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>Data confidence</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>How much of what we hold is trustworthy?</t>
         </is>
       </c>
-      <c r="C6" s="26" t="inlineStr">
+      <c r="C6" s="25" t="inlineStr">
         <is>
           <t>0–1</t>
         </is>
       </c>
-      <c r="D6" s="26" t="inlineStr">
+      <c r="D6" s="25" t="inlineStr">
         <is>
           <t>average field trust × (0.5 + 0.5 × coverage)</t>
         </is>
       </c>
-      <c r="E6" s="26" t="inlineStr">
+      <c r="E6" s="25" t="inlineStr">
         <is>
           <t>Field status: verified 1.0, probable 0.7, stale 0.3, others 0; coverage = share of fit components known</t>
         </is>
       </c>
-      <c r="F6" s="26" t="inlineStr">
+      <c r="F6" s="25" t="inlineStr">
         <is>
           <t>Low confidence raises research priority</t>
         </is>
       </c>
-      <c r="G6" s="31" t="inlineStr">
+      <c r="G6" s="27" t="inlineStr">
         <is>
           <t>System</t>
         </is>
       </c>
-      <c r="H6" s="26" t="inlineStr">
+      <c r="H6" s="25" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>Research priority</t>
         </is>
       </c>
-      <c r="B7" s="26" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>Who is researched first?</t>
         </is>
       </c>
-      <c r="C7" s="26" t="inlineStr">
+      <c r="C7" s="25" t="inlineStr">
         <is>
           <t>low / medium / high</t>
         </is>
       </c>
-      <c r="D7" s="26" t="inlineStr">
+      <c r="D7" s="25" t="inlineStr">
         <is>
           <t>fit × 0.6 + (1 − confidence) × 25 + provider intent × 0.15</t>
         </is>
       </c>
-      <c r="E7" s="26" t="inlineStr">
+      <c r="E7" s="25" t="inlineStr">
         <is>
           <t>Fit, data confidence, third-party intent (none connected yet)</t>
         </is>
       </c>
-      <c r="F7" s="26" t="inlineStr">
+      <c r="F7" s="25" t="inlineStr">
         <is>
           <t>High ≥ 70, medium ≥ 45</t>
         </is>
       </c>
-      <c r="G7" s="31" t="inlineStr">
+      <c r="G7" s="27" t="inlineStr">
         <is>
           <t>System</t>
         </is>
       </c>
-      <c r="H7" s="26" t="inlineStr">
+      <c r="H7" s="25" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="26" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>Intent</t>
         </is>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>Is something happening there now?</t>
         </is>
       </c>
-      <c r="C8" s="26" t="inlineStr">
+      <c r="C8" s="25" t="inlineStr">
         <is>
           <t>0–100; hot / warm / cold</t>
         </is>
       </c>
-      <c r="D8" s="26" t="inlineStr">
+      <c r="D8" s="25" t="inlineStr">
         <is>
           <t>Σ family weight × combined strength + convergence bonus; one family capped at 45</t>
         </is>
       </c>
-      <c r="E8" s="26" t="inlineStr">
+      <c r="E8" s="25" t="inlineStr">
         <is>
           <t>Families (max points, half-life): conversation 28/21d, trigger 26/60d, programme 24/120d, leadership 16/120d, hiring 14/45d, engagement 14/14d, third party 10/21d, team notes 8, negative −40/90d. Strength = status (verified 1, probable 0.65, stale 0.25) × recency × corroboration (1 source 0.75, 2+ = 1)</t>
         </is>
       </c>
-      <c r="F8" s="26" t="inlineStr">
+      <c r="F8" s="25" t="inlineStr">
         <is>
           <t>Bonus: 2 families +5, 3 +12, 4+ +20. Hot ≥ 65 with 2+ families; warm ≥ 35</t>
         </is>
       </c>
-      <c r="G8" s="38" t="inlineStr">
+      <c r="G8" s="28" t="inlineStr">
         <is>
           <t>AI + rules</t>
         </is>
       </c>
-      <c r="H8" s="26" t="inlineStr">
+      <c r="H8" s="25" t="inlineStr">
         <is>
           <t>Fixed (trigger → family mapping per client)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="26" t="inlineStr">
+      <c r="A9" s="25" t="inlineStr">
         <is>
           <t>Engagement</t>
         </is>
       </c>
-      <c r="B9" s="26" t="inlineStr">
+      <c r="B9" s="25" t="inlineStr">
         <is>
           <t>How much are they responding?</t>
         </is>
       </c>
-      <c r="C9" s="26" t="inlineStr">
+      <c r="C9" s="25" t="inlineStr">
         <is>
           <t>0–100</t>
         </is>
       </c>
-      <c r="D9" s="26" t="inlineStr">
+      <c r="D9" s="25" t="inlineStr">
         <is>
           <t>Σ points × 0.5^(age ÷ 14 days); anonymous × 0.5; last 120 days; capped at 100</t>
         </is>
       </c>
-      <c r="E9" s="26" t="inlineStr">
+      <c r="E9" s="25" t="inlineStr">
         <is>
           <t>Reply 50, event 30, pricing visit 25, intent surge 20, download 15, job change 15, site visit 10, click 8, open 2. Each activity counts separately</t>
         </is>
       </c>
-      <c r="F9" s="26" t="inlineStr">
+      <c r="F9" s="25" t="inlineStr">
         <is>
           <t>Aware 10, Engaged 35, MQA 70 (hand-off)</t>
         </is>
       </c>
-      <c r="G9" s="31" t="inlineStr">
+      <c r="G9" s="27" t="inlineStr">
         <is>
           <t>System</t>
         </is>
       </c>
-      <c r="H9" s="26" t="inlineStr">
+      <c r="H9" s="25" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="26" t="inlineStr">
+      <c r="A10" s="25" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="B10" s="26" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>Who does the team work on first?</t>
         </is>
       </c>
-      <c r="C10" s="26" t="inlineStr">
+      <c r="C10" s="25" t="inlineStr">
         <is>
           <t>0–100</t>
         </is>
       </c>
-      <c r="D10" s="26" t="inlineStr">
+      <c r="D10" s="25" t="inlineStr">
         <is>
           <t>(intent × 40 + fit × 30 + value × 20 + timing × 10) ÷ sum of weights</t>
         </is>
       </c>
-      <c r="E10" s="26" t="inlineStr">
+      <c r="E10" s="25" t="inlineStr">
         <is>
           <t>Value = 100 × log10(employees ÷ 1,000) ÷ log10(200); timing = 100 × 0.5^(days since newest signal ÷ 30). Missing fit = 50, missing value = 35</t>
         </is>
       </c>
-      <c r="F10" s="26" t="inlineStr">
+      <c r="F10" s="25" t="inlineStr">
         <is>
           <t>Orders the company list; next best action shown beside it</t>
         </is>
       </c>
-      <c r="G10" s="31" t="inlineStr">
+      <c r="G10" s="27" t="inlineStr">
         <is>
           <t>System</t>
         </is>
       </c>
-      <c r="H10" s="26" t="inlineStr">
+      <c r="H10" s="25" t="inlineStr">
         <is>
           <t>Weights per client (default 40/30/20/10)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="26" t="inlineStr">
+      <c r="A11" s="25" t="inlineStr">
         <is>
           <t>Lookalike fit</t>
         </is>
       </c>
-      <c r="B11" s="26" t="inlineStr">
+      <c r="B11" s="25" t="inlineStr">
         <is>
           <t>How closely does a lookalike match the reference company and need the offering?</t>
         </is>
       </c>
-      <c r="C11" s="26" t="inlineStr">
+      <c r="C11" s="25" t="inlineStr">
         <is>
           <t>0–100</t>
         </is>
       </c>
-      <c r="D11" s="26" t="inlineStr">
+      <c r="D11" s="25" t="inlineStr">
         <is>
           <t>Weighted dimensions rated by AI from evidence</t>
         </is>
       </c>
-      <c r="E11" s="26" t="inlineStr">
+      <c r="E11" s="25" t="inlineStr">
         <is>
           <t>Business model 25%, offering 25%, operations 20%, industry 20%, scale 10%. No verified facts → capped at 50</t>
         </is>
       </c>
-      <c r="F11" s="26" t="inlineStr">
+      <c r="F11" s="25" t="inlineStr">
         <is>
           <t>Recommended from 55. Readiness caps: ready 100, emerging 65, early 35, none 10</t>
         </is>
       </c>
-      <c r="G11" s="38" t="inlineStr">
+      <c r="G11" s="28" t="inlineStr">
         <is>
           <t>AI + rules</t>
         </is>
       </c>
-      <c r="H11" s="26" t="inlineStr">
+      <c r="H11" s="25" t="inlineStr">
         <is>
           <t>Minimum fit, focus and avoid per client; weights fixed</t>
         </is>
@@ -4269,7 +5212,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4333,460 +5276,460 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="45" t="inlineStr">
+      <c r="A5" s="47" t="inlineStr">
         <is>
           <t>E1</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>Upload a CSV and map columns</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t>Which columns mean what; which campaign and sender</t>
         </is>
       </c>
-      <c r="D5" s="26" t="inlineStr">
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>User with access to the client</t>
         </is>
       </c>
-      <c r="E5" s="26" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t>Nothing imported</t>
         </is>
       </c>
-      <c r="F5" s="26" t="inlineStr">
+      <c r="F5" s="25" t="inlineStr">
         <is>
           <t>Import → Upload CSV</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="45" t="inlineStr">
+      <c r="A6" s="47" t="inlineStr">
         <is>
           <t>E2</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>Approve, reject or research a lookalike</t>
         </is>
       </c>
-      <c r="C6" s="26" t="inlineStr">
+      <c r="C6" s="25" t="inlineStr">
         <is>
           <t>Whether the company becomes an account (and may be looked up in Apollo)</t>
         </is>
       </c>
-      <c r="D6" s="26" t="inlineStr">
+      <c r="D6" s="25" t="inlineStr">
         <is>
           <t>User</t>
         </is>
       </c>
-      <c r="E6" s="26" t="inlineStr">
+      <c r="E6" s="25" t="inlineStr">
         <is>
           <t>Stays in "To review"; no contacts looked up</t>
         </is>
       </c>
-      <c r="F6" s="26" t="inlineStr">
+      <c r="F6" s="25" t="inlineStr">
         <is>
           <t>Import → Lookalikes</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="46" t="n">
+      <c r="A7" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="26" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>Confirm a proposed rejection</t>
         </is>
       </c>
-      <c r="C7" s="26" t="inlineStr">
+      <c r="C7" s="25" t="inlineStr">
         <is>
           <t>Reject the company, or override and keep it</t>
         </is>
       </c>
-      <c r="D7" s="26" t="inlineStr">
+      <c r="D7" s="25" t="inlineStr">
         <is>
           <t>User</t>
         </is>
       </c>
-      <c r="E7" s="26" t="inlineStr">
+      <c r="E7" s="25" t="inlineStr">
         <is>
           <t>Company waits in Approvals; not researched further</t>
         </is>
       </c>
-      <c r="F7" s="26" t="inlineStr">
+      <c r="F7" s="25" t="inlineStr">
         <is>
           <t>Approvals</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="46" t="n">
+      <c r="A8" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>Add missing targeting data</t>
         </is>
       </c>
-      <c r="C8" s="26" t="inlineStr">
+      <c r="C8" s="25" t="inlineStr">
         <is>
           <t>Country or employee count the rule needs</t>
         </is>
       </c>
-      <c r="D8" s="26" t="inlineStr">
+      <c r="D8" s="25" t="inlineStr">
         <is>
           <t>User (next upload)</t>
         </is>
       </c>
-      <c r="E8" s="26" t="inlineStr">
+      <c r="E8" s="25" t="inlineStr">
         <is>
           <t>Run stays stopped with the reason</t>
         </is>
       </c>
-      <c r="F8" s="26" t="inlineStr">
+      <c r="F8" s="25" t="inlineStr">
         <is>
           <t>Company page; next CSV</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="46" t="n">
+      <c r="A9" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="26" t="inlineStr">
+      <c r="B9" s="25" t="inlineStr">
         <is>
           <t>Resolve an identity conflict</t>
         </is>
       </c>
-      <c r="C9" s="26" t="inlineStr">
+      <c r="C9" s="25" t="inlineStr">
         <is>
           <t>Which email, title or company is correct</t>
         </is>
       </c>
-      <c r="D9" s="26" t="inlineStr">
+      <c r="D9" s="25" t="inlineStr">
         <is>
           <t>User</t>
         </is>
       </c>
-      <c r="E9" s="26" t="inlineStr">
+      <c r="E9" s="25" t="inlineStr">
         <is>
           <t>Person not contacted</t>
         </is>
       </c>
-      <c r="F9" s="26" t="inlineStr">
+      <c r="F9" s="25" t="inlineStr">
         <is>
           <t>Approvals</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="46" t="n">
+      <c r="A10" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="26" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>Resolve a contradiction</t>
         </is>
       </c>
-      <c r="C10" s="26" t="inlineStr">
+      <c r="C10" s="25" t="inlineStr">
         <is>
           <t>Which fact is right when sources disagree and none is official</t>
         </is>
       </c>
-      <c r="D10" s="26" t="inlineStr">
+      <c r="D10" s="25" t="inlineStr">
         <is>
           <t>User</t>
         </is>
       </c>
-      <c r="E10" s="26" t="inlineStr">
+      <c r="E10" s="25" t="inlineStr">
         <is>
           <t>Question reopens once, then waits</t>
         </is>
       </c>
-      <c r="F10" s="26" t="inlineStr">
+      <c r="F10" s="25" t="inlineStr">
         <is>
           <t>Approvals; company page</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="46" t="n">
+      <c r="A11" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="26" t="inlineStr">
+      <c r="B11" s="25" t="inlineStr">
         <is>
           <t>Human review of a contact</t>
         </is>
       </c>
-      <c r="C11" s="26" t="inlineStr">
+      <c r="C11" s="25" t="inlineStr">
         <is>
           <t>Contact anyway, find someone else, or drop (identity, lawful basis, deliverability, role)</t>
         </is>
       </c>
-      <c r="D11" s="26" t="inlineStr">
+      <c r="D11" s="25" t="inlineStr">
         <is>
           <t>User</t>
         </is>
       </c>
-      <c r="E11" s="26" t="inlineStr">
+      <c r="E11" s="25" t="inlineStr">
         <is>
           <t>Contact not drafted to</t>
         </is>
       </c>
-      <c r="F11" s="26" t="inlineStr">
+      <c r="F11" s="25" t="inlineStr">
         <is>
           <t>Approvals</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="46" t="n">
+      <c r="A12" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="26" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>Approve each draft</t>
         </is>
       </c>
-      <c r="C12" s="26" t="inlineStr">
+      <c r="C12" s="25" t="inlineStr">
         <is>
           <t>Send, edit or reject the email</t>
         </is>
       </c>
-      <c r="D12" s="26" t="inlineStr">
+      <c r="D12" s="25" t="inlineStr">
         <is>
           <t>User</t>
         </is>
       </c>
-      <c r="E12" s="26" t="inlineStr">
+      <c r="E12" s="25" t="inlineStr">
         <is>
           <t>Draft waits; nothing is sent</t>
         </is>
       </c>
-      <c r="F12" s="26" t="inlineStr">
+      <c r="F12" s="25" t="inlineStr">
         <is>
           <t>Approvals; Emails</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="46" t="n">
+      <c r="A13" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="26" t="inlineStr">
+      <c r="B13" s="25" t="inlineStr">
         <is>
           <t>Flag or correct a fact</t>
         </is>
       </c>
-      <c r="C13" s="26" t="inlineStr">
+      <c r="C13" s="25" t="inlineStr">
         <is>
           <t>Mark a fact wrong or give the corrected fact with a source</t>
         </is>
       </c>
-      <c r="D13" s="26" t="inlineStr">
+      <c r="D13" s="25" t="inlineStr">
         <is>
           <t>User</t>
         </is>
       </c>
-      <c r="E13" s="26" t="inlineStr">
+      <c r="E13" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="26" t="inlineStr">
+      <c r="F13" s="25" t="inlineStr">
         <is>
           <t>Company page → Evidence</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="46" t="n">
+      <c r="A14" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="26" t="inlineStr">
+      <c r="B14" s="25" t="inlineStr">
         <is>
           <t>Answer a reply</t>
         </is>
       </c>
-      <c r="C14" s="26" t="inlineStr">
+      <c r="C14" s="25" t="inlineStr">
         <is>
           <t>How to respond (reply assistant suggests)</t>
         </is>
       </c>
-      <c r="D14" s="26" t="inlineStr">
+      <c r="D14" s="25" t="inlineStr">
         <is>
           <t>Account owner</t>
         </is>
       </c>
-      <c r="E14" s="26" t="inlineStr">
+      <c r="E14" s="25" t="inlineStr">
         <is>
           <t>Next best action keeps showing "Answer the reply"</t>
         </is>
       </c>
-      <c r="F14" s="26" t="inlineStr">
+      <c r="F14" s="25" t="inlineStr">
         <is>
           <t>People; Emails</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="46" t="n">
+      <c r="A15" s="23" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="26" t="inlineStr">
+      <c r="B15" s="25" t="inlineStr">
         <is>
           <t>Acknowledge the hand-off</t>
         </is>
       </c>
-      <c r="C15" s="26" t="inlineStr">
+      <c r="C15" s="25" t="inlineStr">
         <is>
           <t>Take the account</t>
         </is>
       </c>
-      <c r="D15" s="26" t="inlineStr">
+      <c r="D15" s="25" t="inlineStr">
         <is>
           <t>Account owner (rep)</t>
         </is>
       </c>
-      <c r="E15" s="26" t="inlineStr">
+      <c r="E15" s="25" t="inlineStr">
         <is>
           <t>Escalated after 24 hours</t>
         </is>
       </c>
-      <c r="F15" s="26" t="inlineStr">
+      <c r="F15" s="25" t="inlineStr">
         <is>
           <t>Hand-offs</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="46" t="n">
+      <c r="A16" s="23" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="26" t="inlineStr">
+      <c r="B16" s="25" t="inlineStr">
         <is>
           <t>Record the outcome</t>
         </is>
       </c>
-      <c r="C16" s="26" t="inlineStr">
+      <c r="C16" s="25" t="inlineStr">
         <is>
           <t>Deal won or lost</t>
         </is>
       </c>
-      <c r="D16" s="26" t="inlineStr">
+      <c r="D16" s="25" t="inlineStr">
         <is>
           <t>Rep / CRM</t>
         </is>
       </c>
-      <c r="E16" s="26" t="inlineStr">
+      <c r="E16" s="25" t="inlineStr">
         <is>
           <t>Learning has no outcome</t>
         </is>
       </c>
-      <c r="F16" s="26" t="inlineStr">
+      <c r="F16" s="25" t="inlineStr">
         <is>
           <t>Opportunities</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="45" t="inlineStr">
+      <c r="A17" s="47" t="inlineStr">
         <is>
           <t>Any</t>
         </is>
       </c>
-      <c r="B17" s="26" t="inlineStr">
+      <c r="B17" s="25" t="inlineStr">
         <is>
           <t>Lock a tier</t>
         </is>
       </c>
-      <c r="C17" s="26" t="inlineStr">
+      <c r="C17" s="25" t="inlineStr">
         <is>
           <t>Keep a tier regardless of size, fit or intent</t>
         </is>
       </c>
-      <c r="D17" s="26" t="inlineStr">
+      <c r="D17" s="25" t="inlineStr">
         <is>
           <t>User</t>
         </is>
       </c>
-      <c r="E17" s="26" t="inlineStr">
+      <c r="E17" s="25" t="inlineStr">
         <is>
           <t>Tier recalculated each run</t>
         </is>
       </c>
-      <c r="F17" s="26" t="inlineStr">
+      <c r="F17" s="25" t="inlineStr">
         <is>
           <t>Company page</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="45" t="inlineStr">
+      <c r="A18" s="47" t="inlineStr">
         <is>
           <t>Setup</t>
         </is>
       </c>
-      <c r="B18" s="26" t="inlineStr">
+      <c r="B18" s="25" t="inlineStr">
         <is>
           <t>Configure the client</t>
         </is>
       </c>
-      <c r="C18" s="26" t="inlineStr">
+      <c r="C18" s="25" t="inlineStr">
         <is>
           <t>ICP, weights, targeting rule, triggers, senders, knowledge base</t>
         </is>
       </c>
-      <c r="D18" s="26" t="inlineStr">
+      <c r="D18" s="25" t="inlineStr">
         <is>
           <t>Super Admin / admin</t>
         </is>
       </c>
-      <c r="E18" s="26" t="inlineStr">
+      <c r="E18" s="25" t="inlineStr">
         <is>
           <t>Defaults apply</t>
         </is>
       </c>
-      <c r="F18" s="26" t="inlineStr">
+      <c r="F18" s="25" t="inlineStr">
         <is>
           <t>Settings; Account Brain</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="45" t="inlineStr">
+      <c r="A19" s="47" t="inlineStr">
         <is>
           <t>Setup</t>
         </is>
       </c>
-      <c r="B19" s="26" t="inlineStr">
+      <c r="B19" s="25" t="inlineStr">
         <is>
           <t>Team and access</t>
         </is>
       </c>
-      <c r="C19" s="26" t="inlineStr">
+      <c r="C19" s="25" t="inlineStr">
         <is>
           <t>Who sees which client accounts</t>
         </is>
       </c>
-      <c r="D19" s="26" t="inlineStr">
+      <c r="D19" s="25" t="inlineStr">
         <is>
           <t>Super Admin</t>
         </is>
       </c>
-      <c r="E19" s="26" t="inlineStr">
+      <c r="E19" s="25" t="inlineStr">
         <is>
           <t>Users see only accounts assigned to them</t>
         </is>
       </c>
-      <c r="F19" s="26" t="inlineStr">
+      <c r="F19" s="25" t="inlineStr">
         <is>
           <t>Team &amp; Access</t>
         </is>
@@ -4802,7 +5745,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4860,297 +5803,297 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>OpenRouter (language model)</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>Reads pages, extracts facts, writes hypotheses, validates them, drafts emails, classifies replies</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t>6, 7, 11, 12; Lookalikes</t>
         </is>
       </c>
-      <c r="D5" s="26" t="inlineStr">
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>Temperature 0.2, fixed JSON schema, one retry. Validator can only lower a hypothesis class</t>
         </is>
       </c>
-      <c r="E5" s="26" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t>Required for research and drafting</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>OpenRouter (embeddings)</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>Meaning-based search in the knowledge base</t>
         </is>
       </c>
-      <c r="C6" s="26" t="inlineStr">
+      <c r="C6" s="25" t="inlineStr">
         <is>
           <t>11; reply assistant</t>
         </is>
       </c>
-      <c r="D6" s="26" t="inlineStr">
+      <c r="D6" s="25" t="inlineStr">
         <is>
           <t>Falls back to word matching if unavailable; drafting never blocks</t>
         </is>
       </c>
-      <c r="E6" s="26" t="inlineStr">
+      <c r="E6" s="25" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="45" t="inlineStr">
+      <c r="A7" s="47" t="inlineStr">
         <is>
           <t>Exa</t>
         </is>
       </c>
-      <c r="B7" s="26" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>Web search for research and lookalike discovery</t>
         </is>
       </c>
-      <c r="C7" s="26" t="inlineStr">
+      <c r="C7" s="25" t="inlineStr">
         <is>
           <t>6; Lookalikes</t>
         </is>
       </c>
-      <c r="D7" s="26" t="inlineStr">
+      <c r="D7" s="25" t="inlineStr">
         <is>
           <t>Cheapest strong sources first; results cached 48h; retries and circuit breaker</t>
         </is>
       </c>
-      <c r="E7" s="26" t="inlineStr">
+      <c r="E7" s="25" t="inlineStr">
         <is>
           <t>One of Exa / Tavily / SerpAPI required</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="26" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>Tavily</t>
         </is>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>Web search</t>
         </is>
       </c>
-      <c r="C8" s="26" t="inlineStr">
+      <c r="C8" s="25" t="inlineStr">
         <is>
           <t>6; Lookalikes</t>
         </is>
       </c>
-      <c r="D8" s="26" t="inlineStr">
+      <c r="D8" s="25" t="inlineStr">
         <is>
           <t>Same as Exa</t>
         </is>
       </c>
-      <c r="E8" s="26" t="inlineStr">
+      <c r="E8" s="25" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="26" t="inlineStr">
+      <c r="A9" s="25" t="inlineStr">
         <is>
           <t>SerpAPI</t>
         </is>
       </c>
-      <c r="B9" s="26" t="inlineStr">
+      <c r="B9" s="25" t="inlineStr">
         <is>
           <t>Web search</t>
         </is>
       </c>
-      <c r="C9" s="26" t="inlineStr">
+      <c r="C9" s="25" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D9" s="26" t="inlineStr">
+      <c r="D9" s="25" t="inlineStr">
         <is>
           <t>Same as Exa</t>
         </is>
       </c>
-      <c r="E9" s="26" t="inlineStr">
+      <c r="E9" s="25" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="26" t="inlineStr">
+      <c r="A10" s="25" t="inlineStr">
         <is>
           <t>Apollo</t>
         </is>
       </c>
-      <c r="B10" s="26" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>People search and contact enrichment; website visitors</t>
         </is>
       </c>
-      <c r="C10" s="26" t="inlineStr">
+      <c r="C10" s="25" t="inlineStr">
         <is>
           <t>9; E3; after lookalike approval</t>
         </is>
       </c>
-      <c r="D10" s="26" t="inlineStr">
+      <c r="D10" s="25" t="inlineStr">
         <is>
           <t>Approval-gated: no people search before a person approves the company. Only for missing fields, within budget</t>
         </is>
       </c>
-      <c r="E10" s="26" t="inlineStr">
+      <c r="E10" s="25" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="26" t="inlineStr">
+      <c r="A11" s="25" t="inlineStr">
         <is>
           <t>MX check (built in)</t>
         </is>
       </c>
-      <c r="B11" s="26" t="inlineStr">
+      <c r="B11" s="25" t="inlineStr">
         <is>
           <t>Email domain accepts mail</t>
         </is>
       </c>
-      <c r="C11" s="26" t="inlineStr">
+      <c r="C11" s="25" t="inlineStr">
         <is>
           <t>9, 10</t>
         </is>
       </c>
-      <c r="D11" s="26" t="inlineStr">
+      <c r="D11" s="25" t="inlineStr">
         <is>
           <t>Free; any email domain accepted</t>
         </is>
       </c>
-      <c r="E11" s="26" t="inlineStr">
+      <c r="E11" s="25" t="inlineStr">
         <is>
           <t>Built in</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="26" t="inlineStr">
+      <c r="A12" s="25" t="inlineStr">
         <is>
           <t>SMTP mailbox</t>
         </is>
       </c>
-      <c r="B12" s="26" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>Sending approved emails</t>
         </is>
       </c>
-      <c r="C12" s="26" t="inlineStr">
+      <c r="C12" s="25" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D12" s="26" t="inlineStr">
+      <c r="D12" s="25" t="inlineStr">
         <is>
           <t>40 per mailbox per day, 400 overall; bounce breaker 2%</t>
         </is>
       </c>
-      <c r="E12" s="26" t="inlineStr">
+      <c r="E12" s="25" t="inlineStr">
         <is>
           <t>Required to send</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="45" t="inlineStr">
+      <c r="A13" s="47" t="inlineStr">
         <is>
           <t>CRM</t>
         </is>
       </c>
-      <c r="B13" s="26" t="inlineStr">
+      <c r="B13" s="25" t="inlineStr">
         <is>
           <t>Opportunities, tasks, contacts; outcomes</t>
         </is>
       </c>
-      <c r="C13" s="26" t="inlineStr">
+      <c r="C13" s="25" t="inlineStr">
         <is>
           <t>3, 13</t>
         </is>
       </c>
-      <c r="D13" s="26" t="inlineStr">
+      <c r="D13" s="25" t="inlineStr">
         <is>
           <t>Customers and open deals are excluded from outreach</t>
         </is>
       </c>
-      <c r="E13" s="26" t="inlineStr">
+      <c r="E13" s="25" t="inlineStr">
         <is>
           <t>Built in</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="26" t="inlineStr">
+      <c r="A14" s="25" t="inlineStr">
         <is>
           <t>Supabase Postgres</t>
         </is>
       </c>
-      <c r="B14" s="26" t="inlineStr">
+      <c r="B14" s="25" t="inlineStr">
         <is>
           <t>All data (schema abm)</t>
         </is>
       </c>
-      <c r="C14" s="26" t="inlineStr">
+      <c r="C14" s="25" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D14" s="26" t="inlineStr">
+      <c r="D14" s="25" t="inlineStr">
         <is>
           <t>Every query scoped to the user's assigned client accounts</t>
         </is>
       </c>
-      <c r="E14" s="26" t="inlineStr">
+      <c r="E14" s="25" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="26" t="inlineStr">
+      <c r="A15" s="25" t="inlineStr">
         <is>
           <t>Vercel</t>
         </is>
       </c>
-      <c r="B15" s="26" t="inlineStr">
+      <c r="B15" s="25" t="inlineStr">
         <is>
           <t>Hosting, background queue, daily schedule</t>
         </is>
       </c>
-      <c r="C15" s="26" t="inlineStr">
+      <c r="C15" s="25" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D15" s="26" t="inlineStr">
+      <c r="D15" s="25" t="inlineStr">
         <is>
           <t>Queue slices up to 5 minutes; watchdog restarts a stopped queue</t>
         </is>
       </c>
-      <c r="E15" s="26" t="inlineStr">
+      <c r="E15" s="25" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -5166,7 +6109,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5218,682 +6161,682 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="45" t="inlineStr">
+      <c r="A5" s="47" t="inlineStr">
         <is>
           <t>Fit</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>Fit weights</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t>Industry 35, size 25, geography 15, partner network 15, tech stack 10</t>
         </is>
       </c>
-      <c r="D5" s="26" t="inlineStr">
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>Per client</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="45" t="inlineStr">
+      <c r="A6" s="47" t="inlineStr">
         <is>
           <t>Fit</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>Industry mode</t>
         </is>
       </c>
-      <c r="C6" s="26" t="inlineStr">
+      <c r="C6" s="25" t="inlineStr">
         <is>
           <t>Manch: any industry (industry not scored)</t>
         </is>
       </c>
-      <c r="D6" s="26" t="inlineStr">
+      <c r="D6" s="25" t="inlineStr">
         <is>
           <t>Per client</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="45" t="inlineStr">
+      <c r="A7" s="47" t="inlineStr">
         <is>
           <t>Fit</t>
         </is>
       </c>
-      <c r="B7" s="26" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>Employee bands</t>
         </is>
       </c>
-      <c r="C7" s="26" t="inlineStr">
+      <c r="C7" s="25" t="inlineStr">
         <is>
           <t>Manch: sweet spot 10,000; mid 5,001; minimum 5,001</t>
         </is>
       </c>
-      <c r="D7" s="26" t="inlineStr">
+      <c r="D7" s="25" t="inlineStr">
         <is>
           <t>Per client</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="45" t="inlineStr">
+      <c r="A8" s="47" t="inlineStr">
         <is>
           <t>Fit</t>
         </is>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>Countries</t>
         </is>
       </c>
-      <c r="C8" s="26" t="inlineStr">
+      <c r="C8" s="25" t="inlineStr">
         <is>
           <t>Manch: primary India; secondary UAE, Saudi Arabia, Qatar, Oman, Kuwait, Bahrain, US, UK, Singapore, Malaysia, Indonesia, Philippines, Australia</t>
         </is>
       </c>
-      <c r="D8" s="26" t="inlineStr">
+      <c r="D8" s="25" t="inlineStr">
         <is>
           <t>Per client</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="45" t="inlineStr">
+      <c r="A9" s="47" t="inlineStr">
         <is>
           <t>Fit</t>
         </is>
       </c>
-      <c r="B9" s="26" t="inlineStr">
+      <c r="B9" s="25" t="inlineStr">
         <is>
           <t>Tech stack lists</t>
         </is>
       </c>
-      <c r="C9" s="26" t="inlineStr">
+      <c r="C9" s="25" t="inlineStr">
         <is>
           <t>ERP, incumbent and workflow tools that count</t>
         </is>
       </c>
-      <c r="D9" s="26" t="inlineStr">
+      <c r="D9" s="25" t="inlineStr">
         <is>
           <t>Per client</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="45" t="inlineStr">
+      <c r="A10" s="47" t="inlineStr">
         <is>
           <t>Fit</t>
         </is>
       </c>
-      <c r="B10" s="26" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>Fit floor</t>
         </is>
       </c>
-      <c r="C10" s="26" t="inlineStr">
+      <c r="C10" s="25" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D10" s="26" t="inlineStr">
+      <c r="D10" s="25" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="45" t="inlineStr">
+      <c r="A11" s="47" t="inlineStr">
         <is>
           <t>Fit</t>
         </is>
       </c>
-      <c r="B11" s="26" t="inlineStr">
+      <c r="B11" s="25" t="inlineStr">
         <is>
           <t>Fit tiers</t>
         </is>
       </c>
-      <c r="C11" s="26" t="inlineStr">
+      <c r="C11" s="25" t="inlineStr">
         <is>
           <t>T1 ≥ 80, T2 ≥ 60</t>
         </is>
       </c>
-      <c r="D11" s="26" t="inlineStr">
+      <c r="D11" s="25" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="26" t="inlineStr">
+      <c r="A12" s="25" t="inlineStr">
         <is>
           <t>Targeting</t>
         </is>
       </c>
-      <c r="B12" s="26" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>Hard targeting rule</t>
         </is>
       </c>
-      <c r="C12" s="26" t="inlineStr">
+      <c r="C12" s="25" t="inlineStr">
         <is>
           <t>Manch: India, more than 5,000 employees</t>
         </is>
       </c>
-      <c r="D12" s="26" t="inlineStr">
+      <c r="D12" s="25" t="inlineStr">
         <is>
           <t>Per client</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="26" t="inlineStr">
+      <c r="A13" s="25" t="inlineStr">
         <is>
           <t>Targeting</t>
         </is>
       </c>
-      <c r="B13" s="26" t="inlineStr">
+      <c r="B13" s="25" t="inlineStr">
         <is>
           <t>Tier by size</t>
         </is>
       </c>
-      <c r="C13" s="26" t="inlineStr">
+      <c r="C13" s="25" t="inlineStr">
         <is>
           <t>Manch: T1 ≥ 50,000, T2 ≥ 15,000 employees</t>
         </is>
       </c>
-      <c r="D13" s="26" t="inlineStr">
+      <c r="D13" s="25" t="inlineStr">
         <is>
           <t>Per client</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="26" t="inlineStr">
+      <c r="A14" s="25" t="inlineStr">
         <is>
           <t>Targeting</t>
         </is>
       </c>
-      <c r="B14" s="26" t="inlineStr">
+      <c r="B14" s="25" t="inlineStr">
         <is>
           <t>Lost-deal cooldown</t>
         </is>
       </c>
-      <c r="C14" s="26" t="inlineStr">
+      <c r="C14" s="25" t="inlineStr">
         <is>
           <t>90 days</t>
         </is>
       </c>
-      <c r="D14" s="26" t="inlineStr">
+      <c r="D14" s="25" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="26" t="inlineStr">
+      <c r="A15" s="25" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="B15" s="26" t="inlineStr">
+      <c r="B15" s="25" t="inlineStr">
         <is>
           <t>Priority weights</t>
         </is>
       </c>
-      <c r="C15" s="26" t="inlineStr">
+      <c r="C15" s="25" t="inlineStr">
         <is>
           <t>Intent 40, fit 30, value 20, timing 10</t>
         </is>
       </c>
-      <c r="D15" s="26" t="inlineStr">
+      <c r="D15" s="25" t="inlineStr">
         <is>
           <t>Per client</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="26" t="inlineStr">
+      <c r="A16" s="25" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="B16" s="26" t="inlineStr">
+      <c r="B16" s="25" t="inlineStr">
         <is>
           <t>Research priority</t>
         </is>
       </c>
-      <c r="C16" s="26" t="inlineStr">
+      <c r="C16" s="25" t="inlineStr">
         <is>
           <t>fit × 0.6 + gap × 25 + intent × 0.15; high ≥ 70, medium ≥ 45</t>
         </is>
       </c>
-      <c r="D16" s="26" t="inlineStr">
+      <c r="D16" s="25" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="26" t="inlineStr">
+      <c r="A17" s="25" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="B17" s="26" t="inlineStr">
+      <c r="B17" s="25" t="inlineStr">
         <is>
           <t>Budget per company</t>
         </is>
       </c>
-      <c r="C17" s="26" t="inlineStr">
+      <c r="C17" s="25" t="inlineStr">
         <is>
           <t>T1 $5.00, T2 $2.00, T3 $0.75 (enforced when budget enforcement is on)</t>
         </is>
       </c>
-      <c r="D17" s="26" t="inlineStr">
+      <c r="D17" s="25" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="26" t="inlineStr">
+      <c r="A18" s="25" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="B18" s="26" t="inlineStr">
+      <c r="B18" s="25" t="inlineStr">
         <is>
           <t>Monthly cap</t>
         </is>
       </c>
-      <c r="C18" s="26" t="inlineStr">
+      <c r="C18" s="25" t="inlineStr">
         <is>
           <t>Per client; warns at 80%</t>
         </is>
       </c>
-      <c r="D18" s="26" t="inlineStr">
+      <c r="D18" s="25" t="inlineStr">
         <is>
           <t>Per client</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="26" t="inlineStr">
+      <c r="A19" s="25" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="B19" s="26" t="inlineStr">
+      <c r="B19" s="25" t="inlineStr">
         <is>
           <t>Investigation rounds / questions</t>
         </is>
       </c>
-      <c r="C19" s="26" t="inlineStr">
+      <c r="C19" s="25" t="inlineStr">
         <is>
           <t>T1 4 / 3, T2 3 / 3, T3 2 / 2</t>
         </is>
       </c>
-      <c r="D19" s="26" t="inlineStr">
+      <c r="D19" s="25" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="26" t="inlineStr">
+      <c r="A20" s="25" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="B20" s="26" t="inlineStr">
+      <c r="B20" s="25" t="inlineStr">
         <is>
           <t>Buying triggers</t>
         </is>
       </c>
-      <c r="C20" s="26" t="inlineStr">
+      <c r="C20" s="25" t="inlineStr">
         <is>
           <t>Keywords and the signal family each feeds</t>
         </is>
       </c>
-      <c r="D20" s="26" t="inlineStr">
+      <c r="D20" s="25" t="inlineStr">
         <is>
           <t>Per client</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="26" t="inlineStr">
+      <c r="A21" s="25" t="inlineStr">
         <is>
           <t>Intent</t>
         </is>
       </c>
-      <c r="B21" s="26" t="inlineStr">
+      <c r="B21" s="25" t="inlineStr">
         <is>
           <t>Hot / warm</t>
         </is>
       </c>
-      <c r="C21" s="26" t="inlineStr">
+      <c r="C21" s="25" t="inlineStr">
         <is>
           <t>Hot ≥ 65 with 2+ families; warm ≥ 35</t>
         </is>
       </c>
-      <c r="D21" s="26" t="inlineStr">
+      <c r="D21" s="25" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="26" t="inlineStr">
+      <c r="A22" s="25" t="inlineStr">
         <is>
           <t>Intent</t>
         </is>
       </c>
-      <c r="B22" s="26" t="inlineStr">
+      <c r="B22" s="25" t="inlineStr">
         <is>
           <t>Surge threshold</t>
         </is>
       </c>
-      <c r="C22" s="26" t="inlineStr">
+      <c r="C22" s="25" t="inlineStr">
         <is>
           <t>60 (pulls a watched account back to research)</t>
         </is>
       </c>
-      <c r="D22" s="26" t="inlineStr">
+      <c r="D22" s="25" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="26" t="inlineStr">
+      <c r="A23" s="25" t="inlineStr">
         <is>
           <t>Readiness</t>
         </is>
       </c>
-      <c r="B23" s="26" t="inlineStr">
+      <c r="B23" s="25" t="inlineStr">
         <is>
           <t>Trigger window</t>
         </is>
       </c>
-      <c r="C23" s="26" t="inlineStr">
+      <c r="C23" s="25" t="inlineStr">
         <is>
           <t>90 days</t>
         </is>
       </c>
-      <c r="D23" s="26" t="inlineStr">
+      <c r="D23" s="25" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="26" t="inlineStr">
+      <c r="A24" s="25" t="inlineStr">
         <is>
           <t>Readiness</t>
         </is>
       </c>
-      <c r="B24" s="26" t="inlineStr">
+      <c r="B24" s="25" t="inlineStr">
         <is>
           <t>Strong evidence</t>
         </is>
       </c>
-      <c r="C24" s="26" t="inlineStr">
+      <c r="C24" s="25" t="inlineStr">
         <is>
           <t>1 verified trigger or 2 independent reports</t>
         </is>
       </c>
-      <c r="D24" s="26" t="inlineStr">
+      <c r="D24" s="25" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="26" t="inlineStr">
+      <c r="A25" s="25" t="inlineStr">
         <is>
           <t>Readiness</t>
         </is>
       </c>
-      <c r="B25" s="26" t="inlineStr">
+      <c r="B25" s="25" t="inlineStr">
         <is>
           <t>Eligible roles</t>
         </is>
       </c>
-      <c r="C25" s="26" t="inlineStr">
+      <c r="C25" s="25" t="inlineStr">
         <is>
           <t>Decision maker, champion</t>
         </is>
       </c>
-      <c r="D25" s="26" t="inlineStr">
+      <c r="D25" s="25" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="45" t="inlineStr">
+      <c r="A26" s="47" t="inlineStr">
         <is>
           <t>Watch</t>
         </is>
       </c>
-      <c r="B26" s="26" t="inlineStr">
+      <c r="B26" s="25" t="inlineStr">
         <is>
           <t>Watch periods</t>
         </is>
       </c>
-      <c r="C26" s="26" t="inlineStr">
+      <c r="C26" s="25" t="inlineStr">
         <is>
           <t>Weak evidence 30 d; negative news 90 d; not now 60 d; lost deal 90 d</t>
         </is>
       </c>
-      <c r="D26" s="26" t="inlineStr">
+      <c r="D26" s="25" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="26" t="inlineStr">
+      <c r="A27" s="25" t="inlineStr">
         <is>
           <t>Engagement</t>
         </is>
       </c>
-      <c r="B27" s="26" t="inlineStr">
+      <c r="B27" s="25" t="inlineStr">
         <is>
           <t>Points per activity</t>
         </is>
       </c>
-      <c r="C27" s="26" t="inlineStr">
+      <c r="C27" s="25" t="inlineStr">
         <is>
           <t>Reply 50, event 30, pricing 25, surge 20, download 15, job change 15, site 10, click 8, open 2</t>
         </is>
       </c>
-      <c r="D27" s="26" t="inlineStr">
+      <c r="D27" s="25" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="26" t="inlineStr">
+      <c r="A28" s="25" t="inlineStr">
         <is>
           <t>Engagement</t>
         </is>
       </c>
-      <c r="B28" s="26" t="inlineStr">
+      <c r="B28" s="25" t="inlineStr">
         <is>
           <t>Decay and weighting</t>
         </is>
       </c>
-      <c r="C28" s="26" t="inlineStr">
+      <c r="C28" s="25" t="inlineStr">
         <is>
           <t>Half-life 14 days; anonymous 50%; window 120 days</t>
         </is>
       </c>
-      <c r="D28" s="26" t="inlineStr">
+      <c r="D28" s="25" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="26" t="inlineStr">
+      <c r="A29" s="25" t="inlineStr">
         <is>
           <t>Engagement</t>
         </is>
       </c>
-      <c r="B29" s="26" t="inlineStr">
+      <c r="B29" s="25" t="inlineStr">
         <is>
           <t>Stage thresholds</t>
         </is>
       </c>
-      <c r="C29" s="26" t="inlineStr">
+      <c r="C29" s="25" t="inlineStr">
         <is>
           <t>Aware 10, Engaged 35, MQA 70</t>
         </is>
       </c>
-      <c r="D29" s="26" t="inlineStr">
+      <c r="D29" s="25" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="26" t="inlineStr">
+      <c r="A30" s="25" t="inlineStr">
         <is>
           <t>Sending</t>
         </is>
       </c>
-      <c r="B30" s="26" t="inlineStr">
+      <c r="B30" s="25" t="inlineStr">
         <is>
           <t>Caps</t>
         </is>
       </c>
-      <c r="C30" s="26" t="inlineStr">
+      <c r="C30" s="25" t="inlineStr">
         <is>
           <t>40 per mailbox per day; 400 overall; bounce breaker 2% after 50 sends</t>
         </is>
       </c>
-      <c r="D30" s="26" t="inlineStr">
+      <c r="D30" s="25" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="26" t="inlineStr">
+      <c r="A31" s="25" t="inlineStr">
         <is>
           <t>Drafting</t>
         </is>
       </c>
-      <c r="B31" s="26" t="inlineStr">
+      <c r="B31" s="25" t="inlineStr">
         <is>
           <t>Guardrail attempts</t>
         </is>
       </c>
-      <c r="C31" s="26" t="inlineStr">
+      <c r="C31" s="25" t="inlineStr">
         <is>
           <t>3, then a person</t>
         </is>
       </c>
-      <c r="D31" s="26" t="inlineStr">
+      <c r="D31" s="25" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="26" t="inlineStr">
+      <c r="A32" s="25" t="inlineStr">
         <is>
           <t>Hand-off</t>
         </is>
       </c>
-      <c r="B32" s="26" t="inlineStr">
+      <c r="B32" s="25" t="inlineStr">
         <is>
           <t>Acknowledge SLA</t>
         </is>
       </c>
-      <c r="C32" s="26" t="inlineStr">
+      <c r="C32" s="25" t="inlineStr">
         <is>
           <t>24 hours</t>
         </is>
       </c>
-      <c r="D32" s="26" t="inlineStr">
+      <c r="D32" s="25" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="26" t="inlineStr">
+      <c r="A33" s="25" t="inlineStr">
         <is>
           <t>Hand-off</t>
         </is>
       </c>
-      <c r="B33" s="26" t="inlineStr">
+      <c r="B33" s="25" t="inlineStr">
         <is>
           <t>Weight retune</t>
         </is>
       </c>
-      <c r="C33" s="26" t="inlineStr">
+      <c r="C33" s="25" t="inlineStr">
         <is>
           <t>After 200 closed deals</t>
         </is>
       </c>
-      <c r="D33" s="26" t="inlineStr">
+      <c r="D33" s="25" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="26" t="inlineStr">
+      <c r="A34" s="25" t="inlineStr">
         <is>
           <t>Lookalikes</t>
         </is>
       </c>
-      <c r="B34" s="26" t="inlineStr">
+      <c r="B34" s="25" t="inlineStr">
         <is>
           <t>Criteria</t>
         </is>
       </c>
-      <c r="C34" s="26" t="inlineStr">
+      <c r="C34" s="25" t="inlineStr">
         <is>
           <t>Focus, avoid, minimum fit 55, 8 candidates, 3 rounds</t>
         </is>
       </c>
-      <c r="D34" s="26" t="inlineStr">
+      <c r="D34" s="25" t="inlineStr">
         <is>
           <t>Per client</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="26" t="inlineStr">
+      <c r="A35" s="25" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="B35" s="26" t="inlineStr">
+      <c r="B35" s="25" t="inlineStr">
         <is>
           <t>Rate limits</t>
         </is>
       </c>
-      <c r="C35" s="26" t="inlineStr">
+      <c r="C35" s="25" t="inlineStr">
         <is>
           <t>Login 10 per 15 min per IP and per email; API 300 per min per IP</t>
         </is>
       </c>
-      <c r="D35" s="26" t="inlineStr">
+      <c r="D35" s="25" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
@@ -5907,423 +6850,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:E18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="20" t="inlineStr">
-        <is>
-          <t>Example Walkthrough</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="21" t="inlineStr">
-        <is>
-          <t>A hypothetical company traced through every stage with the Manch settings. The scores match the worked example in the scoring methodology document.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="22" t="inlineStr">
-        <is>
-          <t>Stage</t>
-        </is>
-      </c>
-      <c r="B4" s="22" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C4" s="22" t="inlineStr">
-        <is>
-          <t>What the system sees</t>
-        </is>
-      </c>
-      <c r="D4" s="22" t="inlineStr">
-        <is>
-          <t>Result</t>
-        </is>
-      </c>
-      <c r="E4" s="22" t="inlineStr">
-        <is>
-          <t>Progress shown in the app</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="45" t="inlineStr">
-        <is>
-          <t>E1</t>
-        </is>
-      </c>
-      <c r="B5" s="26" t="inlineStr">
-        <is>
-          <t>CSV upload</t>
-        </is>
-      </c>
-      <c r="C5" s="26" t="inlineStr">
-        <is>
-          <t>Example Pharma Ltd, India, 8,000 employees, SAP S/4HANA + Power Apps; Head of Procurement among the people</t>
-        </is>
-      </c>
-      <c r="D5" s="26" t="inlineStr">
-        <is>
-          <t>Account and contacts created; journeys started</t>
-        </is>
-      </c>
-      <c r="E5" s="26" t="inlineStr">
-        <is>
-          <t>Imported</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="26" t="inlineStr">
-        <is>
-          <t>Data intake</t>
-        </is>
-      </c>
-      <c r="C6" s="26" t="inlineStr">
-        <is>
-          <t>Fields from the import, source = the file</t>
-        </is>
-      </c>
-      <c r="D6" s="26" t="inlineStr">
-        <is>
-          <t>All fields unknown until checked</t>
-        </is>
-      </c>
-      <c r="E6" s="26" t="inlineStr">
-        <is>
-          <t>Imported</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="26" t="inlineStr">
-        <is>
-          <t>Data clean-up</t>
-        </is>
-      </c>
-      <c r="C7" s="26" t="inlineStr">
-        <is>
-          <t>No duplicates</t>
-        </is>
-      </c>
-      <c r="D7" s="26" t="inlineStr">
-        <is>
-          <t>One account record</t>
-        </is>
-      </c>
-      <c r="E7" s="26" t="inlineStr">
-        <is>
-          <t>Data cleaned</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="46" t="n">
-        <v>3</v>
-      </c>
-      <c r="B8" s="26" t="inlineStr">
-        <is>
-          <t>Fit and tier</t>
-        </is>
-      </c>
-      <c r="C8" s="26" t="inlineStr">
-        <is>
-          <t>Size 18/25 (mid band), geography 15/15, tech 7/10; industry not scored</t>
-        </is>
-      </c>
-      <c r="D8" s="26" t="inlineStr">
-        <is>
-          <t>Fit 80; data confidence 0.61; research priority medium (58); tier T3 by size</t>
-        </is>
-      </c>
-      <c r="E8" s="26" t="inlineStr">
-        <is>
-          <t>Fit checked</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="46" t="n">
-        <v>4</v>
-      </c>
-      <c r="B9" s="26" t="inlineStr">
-        <is>
-          <t>Identity check</t>
-        </is>
-      </c>
-      <c r="C9" s="26" t="inlineStr">
-        <is>
-          <t>Head of Procurement: email, title, company agree</t>
-        </is>
-      </c>
-      <c r="D9" s="26" t="inlineStr">
-        <is>
-          <t>Identity verified</t>
-        </is>
-      </c>
-      <c r="E9" s="26" t="inlineStr">
-        <is>
-          <t>Contacts verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="46" t="n">
-        <v>5</v>
-      </c>
-      <c r="B10" s="26" t="inlineStr">
-        <is>
-          <t>Research plan</t>
-        </is>
-      </c>
-      <c r="C10" s="26" t="inlineStr">
-        <is>
-          <t>Unknown: current programmes, ownership of vendor data</t>
-        </is>
-      </c>
-      <c r="D10" s="26" t="inlineStr">
-        <is>
-          <t>2 questions per round (T3)</t>
-        </is>
-      </c>
-      <c r="E10" s="26" t="inlineStr">
-        <is>
-          <t>Research planned</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="46" t="n">
-        <v>6</v>
-      </c>
-      <c r="B11" s="26" t="inlineStr">
-        <is>
-          <t>Account research</t>
-        </is>
-      </c>
-      <c r="C11" s="26" t="inlineStr">
-        <is>
-          <t>SAP S/4HANA migration (2 sources); MDM lead job post (1 source)</t>
-        </is>
-      </c>
-      <c r="D11" s="26" t="inlineStr">
-        <is>
-          <t>Migration verified; job post probable</t>
-        </is>
-      </c>
-      <c r="E11" s="26" t="inlineStr">
-        <is>
-          <t>Researched</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="46" t="n">
-        <v>7</v>
-      </c>
-      <c r="B12" s="26" t="inlineStr">
-        <is>
-          <t>Twin and intent</t>
-        </is>
-      </c>
-      <c r="C12" s="26" t="inlineStr">
-        <is>
-          <t>Hypothesis linking migration and hiring validated; LinkedIn interest, pricing visit</t>
-        </is>
-      </c>
-      <c r="D12" s="26" t="inlineStr">
-        <is>
-          <t>Intent 83 (hot, 4 families) → tier upgraded T3 → T1, deep dive runs; priority 75</t>
-        </is>
-      </c>
-      <c r="E12" s="26" t="inlineStr">
-        <is>
-          <t>Facts confirmed</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="46" t="n">
-        <v>8</v>
-      </c>
-      <c r="B13" s="26" t="inlineStr">
-        <is>
-          <t>Buying group</t>
-        </is>
-      </c>
-      <c r="C13" s="26" t="inlineStr">
-        <is>
-          <t>Vendor-data problem → procurement and master-data personas</t>
-        </is>
-      </c>
-      <c r="D13" s="26" t="inlineStr">
-        <is>
-          <t>Head of Procurement = decision maker; Head of Master Data = champion</t>
-        </is>
-      </c>
-      <c r="E13" s="26" t="inlineStr">
-        <is>
-          <t>Buying group mapped</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="46" t="n">
-        <v>9</v>
-      </c>
-      <c r="B14" s="26" t="inlineStr">
-        <is>
-          <t>Contact enrichment</t>
-        </is>
-      </c>
-      <c r="C14" s="26" t="inlineStr">
-        <is>
-          <t>Email present; MX check passes</t>
-        </is>
-      </c>
-      <c r="D14" s="26" t="inlineStr">
-        <is>
-          <t>Outreach-ready</t>
-        </is>
-      </c>
-      <c r="E14" s="26" t="inlineStr">
-        <is>
-          <t>Contacts checked</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="46" t="n">
-        <v>10</v>
-      </c>
-      <c r="B15" s="26" t="inlineStr">
-        <is>
-          <t>Readiness</t>
-        </is>
-      </c>
-      <c r="C15" s="26" t="inlineStr">
-        <is>
-          <t>1 verified trigger in 90 days; identity ok; decision maker</t>
-        </is>
-      </c>
-      <c r="D15" s="26" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="E15" s="26" t="inlineStr">
-        <is>
-          <t>Ready for outreach</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="46" t="n">
-        <v>11</v>
-      </c>
-      <c r="B16" s="26" t="inlineStr">
-        <is>
-          <t>Draft and approve</t>
-        </is>
-      </c>
-      <c r="C16" s="26" t="inlineStr">
-        <is>
-          <t>Brief + cited migration fact + knowledge base (vendor onboarding use case, "mid-migration" objection)</t>
-        </is>
-      </c>
-      <c r="D16" s="26" t="inlineStr">
-        <is>
-          <t>Draft passes guardrails; user approves</t>
-        </is>
-      </c>
-      <c r="E16" s="26" t="inlineStr">
-        <is>
-          <t>Emails drafted</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="46" t="n">
-        <v>12</v>
-      </c>
-      <c r="B17" s="26" t="inlineStr">
-        <is>
-          <t>Send and score</t>
-        </is>
-      </c>
-      <c r="C17" s="26" t="inlineStr">
-        <is>
-          <t>Email sent; click, 2 opens, pricing visit, anonymous site visit</t>
-        </is>
-      </c>
-      <c r="D17" s="26" t="inlineStr">
-        <is>
-          <t>Engagement 35.3 → Engaged; next best action: call the Head of Procurement</t>
-        </is>
-      </c>
-      <c r="E17" s="26" t="inlineStr">
-        <is>
-          <t>In outreach</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="46" t="n">
-        <v>13</v>
-      </c>
-      <c r="B18" s="26" t="inlineStr">
-        <is>
-          <t>Hand-off</t>
-        </is>
-      </c>
-      <c r="C18" s="26" t="inlineStr">
-        <is>
-          <t>Prospect replies positively (or engagement reaches 70)</t>
-        </is>
-      </c>
-      <c r="D18" s="26" t="inlineStr">
-        <is>
-          <t>Hand-off with briefing; outreach paused; rep acknowledges within 24h</t>
-        </is>
-      </c>
-      <c r="E18" s="26" t="inlineStr">
-        <is>
-          <t>Handed to sales</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A4:E18"/>
-  <mergeCells count="1">
-    <mergeCell ref="A2:E2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
 </file>